--- a/Modaliteter/FTV/accu_table.xlsx
+++ b/Modaliteter/FTV/accu_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vlladmin-my.sharepoint.com/personal/max_hellstrom_regionvasterbotten_se/Documents/10 - cases/20260217 - cbct_opt_odr/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\rvbrtg\Modaliteter\FTV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="816" documentId="11_F25DC773A252ABDACC104806D9DF56305BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEEEA19D-333E-4B33-AB46-07924875D9B5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CFE62E-E614-4887-ABB3-CE68725BF1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="17">
   <si>
     <t>Mode</t>
   </si>
@@ -144,10 +144,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.5703125" customWidth="1"/>
@@ -1181,8 +1177,8 @@
       <c r="G21" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="1">
-        <v>71.8</v>
+      <c r="H21">
+        <v>63.2</v>
       </c>
       <c r="I21">
         <f t="shared" si="0"/>
@@ -1219,7 +1215,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>108</v>
+        <v>94.9</v>
       </c>
       <c r="I22">
         <f t="shared" si="0"/>
@@ -1256,7 +1252,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="I23">
         <f t="shared" si="0"/>
@@ -1293,7 +1289,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="I24">
         <f t="shared" si="0"/>
@@ -1330,7 +1326,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="I25">
         <f t="shared" si="0"/>
@@ -1367,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="I26">
         <f t="shared" si="0"/>
@@ -1404,7 +1400,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="I27">
         <f t="shared" si="0"/>
@@ -1441,7 +1437,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>323</v>
+        <v>285</v>
       </c>
       <c r="I28">
         <f t="shared" si="0"/>
@@ -1478,7 +1474,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="I29">
         <f t="shared" si="0"/>
@@ -1515,7 +1511,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>395</v>
+        <v>348</v>
       </c>
       <c r="I30">
         <f t="shared" si="0"/>
@@ -1552,7 +1548,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="I31">
         <f t="shared" si="0"/>
@@ -1589,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>467</v>
+        <v>411</v>
       </c>
       <c r="I32">
         <f t="shared" si="0"/>
@@ -1626,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="I33">
         <f t="shared" si="0"/>
@@ -1663,7 +1659,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>539</v>
+        <v>474</v>
       </c>
       <c r="I34">
         <f t="shared" si="0"/>
@@ -1700,7 +1696,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>575</v>
+        <v>506</v>
       </c>
       <c r="I35">
         <f t="shared" si="0"/>
@@ -1737,7 +1733,7 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>71.8</v>
+        <v>63.2</v>
       </c>
       <c r="I36">
         <f t="shared" si="0"/>
@@ -1774,7 +1770,7 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>108</v>
+        <v>94.9</v>
       </c>
       <c r="I37">
         <f t="shared" si="0"/>
@@ -1811,7 +1807,7 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="I38">
         <f t="shared" si="0"/>
@@ -1848,7 +1844,7 @@
         <v>7</v>
       </c>
       <c r="H39">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="I39">
         <f t="shared" si="0"/>
@@ -1885,7 +1881,7 @@
         <v>7</v>
       </c>
       <c r="H40">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="I40">
         <f t="shared" si="0"/>
@@ -1922,7 +1918,7 @@
         <v>7</v>
       </c>
       <c r="H41">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="I41">
         <f t="shared" si="0"/>
@@ -1959,7 +1955,7 @@
         <v>7</v>
       </c>
       <c r="H42">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="I42">
         <f t="shared" si="0"/>
@@ -1996,7 +1992,7 @@
         <v>7</v>
       </c>
       <c r="H43">
-        <v>323</v>
+        <v>285</v>
       </c>
       <c r="I43">
         <f t="shared" si="0"/>
@@ -2033,7 +2029,7 @@
         <v>7</v>
       </c>
       <c r="H44">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="I44">
         <f t="shared" si="0"/>
@@ -2070,7 +2066,7 @@
         <v>7</v>
       </c>
       <c r="H45">
-        <v>395</v>
+        <v>348</v>
       </c>
       <c r="I45">
         <f t="shared" si="0"/>
@@ -2107,7 +2103,7 @@
         <v>7</v>
       </c>
       <c r="H46">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="I46">
         <f t="shared" si="0"/>
@@ -2144,7 +2140,7 @@
         <v>7</v>
       </c>
       <c r="H47">
-        <v>467</v>
+        <v>411</v>
       </c>
       <c r="I47">
         <f t="shared" si="0"/>
@@ -2181,7 +2177,7 @@
         <v>7</v>
       </c>
       <c r="H48">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="I48">
         <f t="shared" si="0"/>
@@ -2218,7 +2214,7 @@
         <v>7</v>
       </c>
       <c r="H49">
-        <v>539</v>
+        <v>474</v>
       </c>
       <c r="I49">
         <f t="shared" si="0"/>
@@ -2255,7 +2251,7 @@
         <v>7</v>
       </c>
       <c r="H50">
-        <v>575</v>
+        <v>506</v>
       </c>
       <c r="I50">
         <f t="shared" si="0"/>
@@ -3697,9 +3693,6 @@
       <c r="G89" t="s">
         <v>7</v>
       </c>
-      <c r="H89">
-        <v>140</v>
-      </c>
       <c r="I89">
         <f t="shared" si="2"/>
         <v>30.8</v>
@@ -3734,9 +3727,6 @@
       <c r="G90" t="s">
         <v>7</v>
       </c>
-      <c r="H90">
-        <v>210</v>
-      </c>
       <c r="I90">
         <f t="shared" si="2"/>
         <v>46.2</v>
@@ -3771,9 +3761,6 @@
       <c r="G91" t="s">
         <v>7</v>
       </c>
-      <c r="H91">
-        <v>280</v>
-      </c>
       <c r="I91">
         <f t="shared" si="2"/>
         <v>61.6</v>
@@ -3808,9 +3795,6 @@
       <c r="G92" t="s">
         <v>7</v>
       </c>
-      <c r="H92">
-        <v>349</v>
-      </c>
       <c r="I92">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -3845,9 +3829,6 @@
       <c r="G93" t="s">
         <v>7</v>
       </c>
-      <c r="H93">
-        <v>419</v>
-      </c>
       <c r="I93">
         <f t="shared" si="2"/>
         <v>92.4</v>
@@ -3882,9 +3863,6 @@
       <c r="G94" t="s">
         <v>7</v>
       </c>
-      <c r="H94">
-        <v>489</v>
-      </c>
       <c r="I94">
         <f t="shared" si="2"/>
         <v>107.8</v>
@@ -3919,9 +3897,6 @@
       <c r="G95" t="s">
         <v>7</v>
       </c>
-      <c r="H95">
-        <v>559</v>
-      </c>
       <c r="I95">
         <f t="shared" si="2"/>
         <v>123.2</v>
@@ -3956,9 +3931,6 @@
       <c r="G96" t="s">
         <v>7</v>
       </c>
-      <c r="H96">
-        <v>629</v>
-      </c>
       <c r="I96">
         <f t="shared" si="2"/>
         <v>138.6</v>
@@ -3993,9 +3965,6 @@
       <c r="G97" t="s">
         <v>7</v>
       </c>
-      <c r="H97">
-        <v>699</v>
-      </c>
       <c r="I97">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -4030,9 +3999,6 @@
       <c r="G98" t="s">
         <v>7</v>
       </c>
-      <c r="H98">
-        <v>769</v>
-      </c>
       <c r="I98">
         <f t="shared" si="2"/>
         <v>169.4</v>
@@ -4067,9 +4033,6 @@
       <c r="G99" t="s">
         <v>7</v>
       </c>
-      <c r="H99">
-        <v>839</v>
-      </c>
       <c r="I99">
         <f t="shared" si="2"/>
         <v>184.8</v>
@@ -4104,9 +4067,6 @@
       <c r="G100" t="s">
         <v>7</v>
       </c>
-      <c r="H100">
-        <v>908</v>
-      </c>
       <c r="I100">
         <f t="shared" si="2"/>
         <v>200.20000000000002</v>
@@ -4141,9 +4101,6 @@
       <c r="G101" t="s">
         <v>7</v>
       </c>
-      <c r="H101">
-        <v>978</v>
-      </c>
       <c r="I101">
         <f t="shared" si="2"/>
         <v>215.6</v>
@@ -4178,9 +4135,6 @@
       <c r="G102" t="s">
         <v>7</v>
       </c>
-      <c r="H102">
-        <v>1050</v>
-      </c>
       <c r="I102">
         <f t="shared" si="2"/>
         <v>231</v>
@@ -4215,9 +4169,6 @@
       <c r="G103" t="s">
         <v>7</v>
       </c>
-      <c r="H103">
-        <v>1120</v>
-      </c>
       <c r="I103">
         <f t="shared" si="2"/>
         <v>246.4</v>
@@ -4252,9 +4203,6 @@
       <c r="G104" t="s">
         <v>7</v>
       </c>
-      <c r="H104">
-        <v>140</v>
-      </c>
       <c r="I104">
         <f t="shared" si="2"/>
         <v>30.8</v>
@@ -4289,9 +4237,6 @@
       <c r="G105" t="s">
         <v>7</v>
       </c>
-      <c r="H105">
-        <v>210</v>
-      </c>
       <c r="I105">
         <f t="shared" si="2"/>
         <v>46.2</v>
@@ -4326,9 +4271,6 @@
       <c r="G106" t="s">
         <v>7</v>
       </c>
-      <c r="H106">
-        <v>280</v>
-      </c>
       <c r="I106">
         <f t="shared" si="2"/>
         <v>61.6</v>
@@ -4363,9 +4305,6 @@
       <c r="G107" t="s">
         <v>7</v>
       </c>
-      <c r="H107">
-        <v>349</v>
-      </c>
       <c r="I107">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -4400,9 +4339,6 @@
       <c r="G108" t="s">
         <v>7</v>
       </c>
-      <c r="H108">
-        <v>419</v>
-      </c>
       <c r="I108">
         <f t="shared" si="2"/>
         <v>92.4</v>
@@ -4437,9 +4373,6 @@
       <c r="G109" t="s">
         <v>7</v>
       </c>
-      <c r="H109">
-        <v>489</v>
-      </c>
       <c r="I109">
         <f t="shared" si="2"/>
         <v>107.8</v>
@@ -4474,9 +4407,6 @@
       <c r="G110" t="s">
         <v>7</v>
       </c>
-      <c r="H110">
-        <v>559</v>
-      </c>
       <c r="I110">
         <f t="shared" si="2"/>
         <v>123.2</v>
@@ -4511,9 +4441,6 @@
       <c r="G111" t="s">
         <v>7</v>
       </c>
-      <c r="H111">
-        <v>629</v>
-      </c>
       <c r="I111">
         <f t="shared" si="2"/>
         <v>138.6</v>
@@ -4548,9 +4475,6 @@
       <c r="G112" t="s">
         <v>7</v>
       </c>
-      <c r="H112">
-        <v>699</v>
-      </c>
       <c r="I112">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -4585,9 +4509,6 @@
       <c r="G113" t="s">
         <v>7</v>
       </c>
-      <c r="H113">
-        <v>769</v>
-      </c>
       <c r="I113">
         <f t="shared" si="2"/>
         <v>169.4</v>
@@ -4622,9 +4543,6 @@
       <c r="G114" t="s">
         <v>7</v>
       </c>
-      <c r="H114">
-        <v>839</v>
-      </c>
       <c r="I114">
         <f t="shared" si="2"/>
         <v>184.8</v>
@@ -4659,9 +4577,6 @@
       <c r="G115" t="s">
         <v>7</v>
       </c>
-      <c r="H115">
-        <v>908</v>
-      </c>
       <c r="I115">
         <f t="shared" si="2"/>
         <v>200.20000000000002</v>
@@ -4696,9 +4611,6 @@
       <c r="G116" t="s">
         <v>7</v>
       </c>
-      <c r="H116">
-        <v>978</v>
-      </c>
       <c r="I116">
         <f t="shared" si="2"/>
         <v>215.6</v>
@@ -4733,9 +4645,6 @@
       <c r="G117" t="s">
         <v>7</v>
       </c>
-      <c r="H117">
-        <v>1050</v>
-      </c>
       <c r="I117">
         <f t="shared" si="2"/>
         <v>231</v>
@@ -4770,9 +4679,6 @@
       <c r="G118" t="s">
         <v>7</v>
       </c>
-      <c r="H118">
-        <v>1120</v>
-      </c>
       <c r="I118">
         <f t="shared" si="2"/>
         <v>246.4</v>
@@ -4807,9 +4713,6 @@
       <c r="G119" t="s">
         <v>7</v>
       </c>
-      <c r="H119">
-        <v>47.6</v>
-      </c>
       <c r="I119">
         <f t="shared" si="2"/>
         <v>10.5</v>
@@ -4844,9 +4747,6 @@
       <c r="G120" t="s">
         <v>7</v>
       </c>
-      <c r="H120">
-        <v>71.5</v>
-      </c>
       <c r="I120">
         <f t="shared" si="2"/>
         <v>15.75</v>
@@ -4881,9 +4781,6 @@
       <c r="G121" t="s">
         <v>7</v>
       </c>
-      <c r="H121">
-        <v>95.3</v>
-      </c>
       <c r="I121">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -4918,9 +4815,6 @@
       <c r="G122" t="s">
         <v>7</v>
       </c>
-      <c r="H122">
-        <v>119</v>
-      </c>
       <c r="I122">
         <f t="shared" si="2"/>
         <v>26.25</v>
@@ -4955,9 +4849,6 @@
       <c r="G123" t="s">
         <v>7</v>
       </c>
-      <c r="H123">
-        <v>143</v>
-      </c>
       <c r="I123">
         <f t="shared" si="2"/>
         <v>31.5</v>
@@ -4992,9 +4883,6 @@
       <c r="G124" t="s">
         <v>7</v>
       </c>
-      <c r="H124">
-        <v>167</v>
-      </c>
       <c r="I124">
         <f t="shared" si="2"/>
         <v>36.75</v>
@@ -5029,9 +4917,6 @@
       <c r="G125" t="s">
         <v>7</v>
       </c>
-      <c r="H125">
-        <v>191</v>
-      </c>
       <c r="I125">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -5066,9 +4951,6 @@
       <c r="G126" t="s">
         <v>7</v>
       </c>
-      <c r="H126">
-        <v>214</v>
-      </c>
       <c r="I126">
         <f t="shared" si="2"/>
         <v>47.25</v>
@@ -5103,9 +4985,6 @@
       <c r="G127" t="s">
         <v>7</v>
       </c>
-      <c r="H127">
-        <v>238</v>
-      </c>
       <c r="I127">
         <f t="shared" si="2"/>
         <v>52.5</v>
@@ -5140,9 +5019,6 @@
       <c r="G128" t="s">
         <v>7</v>
       </c>
-      <c r="H128">
-        <v>262</v>
-      </c>
       <c r="I128">
         <f t="shared" si="2"/>
         <v>57.75</v>
@@ -5177,9 +5053,6 @@
       <c r="G129" t="s">
         <v>7</v>
       </c>
-      <c r="H129">
-        <v>286</v>
-      </c>
       <c r="I129">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -5214,9 +5087,6 @@
       <c r="G130" t="s">
         <v>7</v>
       </c>
-      <c r="H130">
-        <v>310</v>
-      </c>
       <c r="I130">
         <f t="shared" si="2"/>
         <v>68.25</v>
@@ -5251,9 +5121,6 @@
       <c r="G131" t="s">
         <v>7</v>
       </c>
-      <c r="H131">
-        <v>334</v>
-      </c>
       <c r="I131">
         <f t="shared" ref="I131:I137" si="4">C131*F131</f>
         <v>73.5</v>
@@ -5288,9 +5155,6 @@
       <c r="G132" t="s">
         <v>7</v>
       </c>
-      <c r="H132">
-        <v>357</v>
-      </c>
       <c r="I132">
         <f t="shared" si="4"/>
         <v>78.75</v>
@@ -5325,9 +5189,6 @@
       <c r="G133" t="s">
         <v>7</v>
       </c>
-      <c r="H133">
-        <v>381</v>
-      </c>
       <c r="I133">
         <f t="shared" si="4"/>
         <v>84</v>
@@ -5362,9 +5223,6 @@
       <c r="G134" t="s">
         <v>7</v>
       </c>
-      <c r="H134">
-        <v>405</v>
-      </c>
       <c r="I134">
         <f t="shared" si="4"/>
         <v>89.25</v>
@@ -5399,9 +5257,6 @@
       <c r="G135" t="s">
         <v>7</v>
       </c>
-      <c r="H135">
-        <v>429</v>
-      </c>
       <c r="I135">
         <f t="shared" si="4"/>
         <v>94.5</v>
@@ -5436,9 +5291,6 @@
       <c r="G136" t="s">
         <v>7</v>
       </c>
-      <c r="H136">
-        <v>453</v>
-      </c>
       <c r="I136">
         <f t="shared" si="4"/>
         <v>99.75</v>
@@ -5473,9 +5325,6 @@
       <c r="G137" t="s">
         <v>7</v>
       </c>
-      <c r="H137">
-        <v>476</v>
-      </c>
       <c r="I137">
         <f t="shared" si="4"/>
         <v>105</v>
@@ -5485,6 +5334,4924 @@
       </c>
       <c r="K137" s="2">
         <f t="shared" si="5"/>
+        <v>194.44444444444446</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138">
+        <v>180</v>
+      </c>
+      <c r="C138" s="1">
+        <v>9</v>
+      </c>
+      <c r="D138" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138">
+        <v>90</v>
+      </c>
+      <c r="F138" s="1">
+        <v>1</v>
+      </c>
+      <c r="G138" t="s">
+        <v>7</v>
+      </c>
+      <c r="H138" s="1">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="I138">
+        <f>C138*F138</f>
+        <v>9</v>
+      </c>
+      <c r="J138">
+        <v>256</v>
+      </c>
+      <c r="K138" s="2">
+        <f>1000*I138/J138</f>
+        <v>35.15625</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139">
+        <v>180</v>
+      </c>
+      <c r="C139" s="1">
+        <v>9</v>
+      </c>
+      <c r="D139" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139">
+        <v>90</v>
+      </c>
+      <c r="F139" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G139" t="s">
+        <v>7</v>
+      </c>
+      <c r="H139">
+        <v>61.3</v>
+      </c>
+      <c r="I139">
+        <f t="shared" ref="I139:I202" si="6">C139*F139</f>
+        <v>13.5</v>
+      </c>
+      <c r="J139">
+        <v>256</v>
+      </c>
+      <c r="K139" s="2">
+        <f t="shared" ref="K139:K202" si="7">1000*I139/J139</f>
+        <v>52.734375</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140">
+        <v>180</v>
+      </c>
+      <c r="C140" s="1">
+        <v>9</v>
+      </c>
+      <c r="D140" t="s">
+        <v>10</v>
+      </c>
+      <c r="E140">
+        <v>90</v>
+      </c>
+      <c r="F140" s="1">
+        <v>2</v>
+      </c>
+      <c r="G140" t="s">
+        <v>7</v>
+      </c>
+      <c r="H140">
+        <v>81.7</v>
+      </c>
+      <c r="I140">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="J140">
+        <v>256</v>
+      </c>
+      <c r="K140" s="2">
+        <f t="shared" si="7"/>
+        <v>70.3125</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141">
+        <v>180</v>
+      </c>
+      <c r="C141" s="1">
+        <v>9</v>
+      </c>
+      <c r="D141" t="s">
+        <v>10</v>
+      </c>
+      <c r="E141">
+        <v>90</v>
+      </c>
+      <c r="F141" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G141" t="s">
+        <v>7</v>
+      </c>
+      <c r="H141">
+        <v>102</v>
+      </c>
+      <c r="I141">
+        <f t="shared" si="6"/>
+        <v>22.5</v>
+      </c>
+      <c r="J141">
+        <v>256</v>
+      </c>
+      <c r="K141" s="2">
+        <f t="shared" si="7"/>
+        <v>87.890625</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142">
+        <v>180</v>
+      </c>
+      <c r="C142" s="1">
+        <v>9</v>
+      </c>
+      <c r="D142" t="s">
+        <v>10</v>
+      </c>
+      <c r="E142">
+        <v>90</v>
+      </c>
+      <c r="F142" s="1">
+        <v>3</v>
+      </c>
+      <c r="G142" t="s">
+        <v>7</v>
+      </c>
+      <c r="H142">
+        <v>123</v>
+      </c>
+      <c r="I142">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="J142">
+        <v>256</v>
+      </c>
+      <c r="K142" s="2">
+        <f t="shared" si="7"/>
+        <v>105.46875</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>8</v>
+      </c>
+      <c r="B143">
+        <v>180</v>
+      </c>
+      <c r="C143" s="1">
+        <v>9</v>
+      </c>
+      <c r="D143" t="s">
+        <v>10</v>
+      </c>
+      <c r="E143">
+        <v>90</v>
+      </c>
+      <c r="F143" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G143" t="s">
+        <v>7</v>
+      </c>
+      <c r="H143">
+        <v>143</v>
+      </c>
+      <c r="I143">
+        <f t="shared" si="6"/>
+        <v>31.5</v>
+      </c>
+      <c r="J143">
+        <v>256</v>
+      </c>
+      <c r="K143" s="2">
+        <f t="shared" si="7"/>
+        <v>123.046875</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144">
+        <v>180</v>
+      </c>
+      <c r="C144" s="1">
+        <v>9</v>
+      </c>
+      <c r="D144" t="s">
+        <v>10</v>
+      </c>
+      <c r="E144">
+        <v>90</v>
+      </c>
+      <c r="F144" s="1">
+        <v>4</v>
+      </c>
+      <c r="G144" t="s">
+        <v>7</v>
+      </c>
+      <c r="H144">
+        <v>163</v>
+      </c>
+      <c r="I144">
+        <f t="shared" si="6"/>
+        <v>36</v>
+      </c>
+      <c r="J144">
+        <v>256</v>
+      </c>
+      <c r="K144" s="2">
+        <f t="shared" si="7"/>
+        <v>140.625</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145">
+        <v>180</v>
+      </c>
+      <c r="C145" s="1">
+        <v>9</v>
+      </c>
+      <c r="D145" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145">
+        <v>90</v>
+      </c>
+      <c r="F145" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G145" t="s">
+        <v>7</v>
+      </c>
+      <c r="H145">
+        <v>184</v>
+      </c>
+      <c r="I145">
+        <f t="shared" si="6"/>
+        <v>40.5</v>
+      </c>
+      <c r="J145">
+        <v>256</v>
+      </c>
+      <c r="K145" s="2">
+        <f t="shared" si="7"/>
+        <v>158.203125</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146">
+        <v>180</v>
+      </c>
+      <c r="C146" s="1">
+        <v>9</v>
+      </c>
+      <c r="D146" t="s">
+        <v>10</v>
+      </c>
+      <c r="E146">
+        <v>90</v>
+      </c>
+      <c r="F146" s="1">
+        <v>5</v>
+      </c>
+      <c r="G146" t="s">
+        <v>7</v>
+      </c>
+      <c r="H146">
+        <v>204</v>
+      </c>
+      <c r="I146">
+        <f t="shared" si="6"/>
+        <v>45</v>
+      </c>
+      <c r="J146">
+        <v>256</v>
+      </c>
+      <c r="K146" s="2">
+        <f t="shared" si="7"/>
+        <v>175.78125</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147">
+        <v>180</v>
+      </c>
+      <c r="C147" s="1">
+        <v>9</v>
+      </c>
+      <c r="D147" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147">
+        <v>90</v>
+      </c>
+      <c r="F147" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G147" t="s">
+        <v>7</v>
+      </c>
+      <c r="H147">
+        <v>225</v>
+      </c>
+      <c r="I147">
+        <f t="shared" si="6"/>
+        <v>49.5</v>
+      </c>
+      <c r="J147">
+        <v>256</v>
+      </c>
+      <c r="K147" s="2">
+        <f t="shared" si="7"/>
+        <v>193.359375</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148">
+        <v>180</v>
+      </c>
+      <c r="C148" s="1">
+        <v>9</v>
+      </c>
+      <c r="D148" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148">
+        <v>90</v>
+      </c>
+      <c r="F148" s="1">
+        <v>6</v>
+      </c>
+      <c r="G148" t="s">
+        <v>7</v>
+      </c>
+      <c r="H148">
+        <v>245</v>
+      </c>
+      <c r="I148">
+        <f t="shared" si="6"/>
+        <v>54</v>
+      </c>
+      <c r="J148">
+        <v>256</v>
+      </c>
+      <c r="K148" s="2">
+        <f t="shared" si="7"/>
+        <v>210.9375</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>8</v>
+      </c>
+      <c r="B149">
+        <v>180</v>
+      </c>
+      <c r="C149" s="1">
+        <v>9</v>
+      </c>
+      <c r="D149" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149">
+        <v>90</v>
+      </c>
+      <c r="F149" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G149" t="s">
+        <v>7</v>
+      </c>
+      <c r="H149">
+        <v>265</v>
+      </c>
+      <c r="I149">
+        <f t="shared" si="6"/>
+        <v>58.5</v>
+      </c>
+      <c r="J149">
+        <v>256</v>
+      </c>
+      <c r="K149" s="2">
+        <f t="shared" si="7"/>
+        <v>228.515625</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>8</v>
+      </c>
+      <c r="B150">
+        <v>180</v>
+      </c>
+      <c r="C150" s="1">
+        <v>9</v>
+      </c>
+      <c r="D150" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150">
+        <v>90</v>
+      </c>
+      <c r="F150" s="1">
+        <v>7</v>
+      </c>
+      <c r="G150" t="s">
+        <v>7</v>
+      </c>
+      <c r="H150">
+        <v>286</v>
+      </c>
+      <c r="I150">
+        <f t="shared" si="6"/>
+        <v>63</v>
+      </c>
+      <c r="J150">
+        <v>256</v>
+      </c>
+      <c r="K150" s="2">
+        <f t="shared" si="7"/>
+        <v>246.09375</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151">
+        <v>180</v>
+      </c>
+      <c r="C151" s="1">
+        <v>9</v>
+      </c>
+      <c r="D151" t="s">
+        <v>10</v>
+      </c>
+      <c r="E151">
+        <v>90</v>
+      </c>
+      <c r="F151" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G151" t="s">
+        <v>7</v>
+      </c>
+      <c r="H151">
+        <v>306</v>
+      </c>
+      <c r="I151">
+        <f t="shared" si="6"/>
+        <v>67.5</v>
+      </c>
+      <c r="J151">
+        <v>256</v>
+      </c>
+      <c r="K151" s="2">
+        <f t="shared" si="7"/>
+        <v>263.671875</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152">
+        <v>180</v>
+      </c>
+      <c r="C152" s="1">
+        <v>9</v>
+      </c>
+      <c r="D152" t="s">
+        <v>10</v>
+      </c>
+      <c r="E152">
+        <v>90</v>
+      </c>
+      <c r="F152" s="1">
+        <v>8</v>
+      </c>
+      <c r="G152" t="s">
+        <v>7</v>
+      </c>
+      <c r="H152">
+        <v>327</v>
+      </c>
+      <c r="I152">
+        <f t="shared" si="6"/>
+        <v>72</v>
+      </c>
+      <c r="J152">
+        <v>256</v>
+      </c>
+      <c r="K152" s="2">
+        <f t="shared" si="7"/>
+        <v>281.25</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>8</v>
+      </c>
+      <c r="B153">
+        <v>180</v>
+      </c>
+      <c r="C153" s="1">
+        <v>9</v>
+      </c>
+      <c r="D153" t="s">
+        <v>10</v>
+      </c>
+      <c r="E153">
+        <v>90</v>
+      </c>
+      <c r="F153" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G153" t="s">
+        <v>7</v>
+      </c>
+      <c r="H153">
+        <v>347</v>
+      </c>
+      <c r="I153">
+        <f t="shared" si="6"/>
+        <v>76.5</v>
+      </c>
+      <c r="J153">
+        <v>256</v>
+      </c>
+      <c r="K153" s="2">
+        <f t="shared" si="7"/>
+        <v>298.828125</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154">
+        <v>180</v>
+      </c>
+      <c r="C154" s="1">
+        <v>9</v>
+      </c>
+      <c r="D154" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154">
+        <v>90</v>
+      </c>
+      <c r="F154" s="1">
+        <v>9</v>
+      </c>
+      <c r="G154" t="s">
+        <v>7</v>
+      </c>
+      <c r="H154">
+        <v>368</v>
+      </c>
+      <c r="I154">
+        <f t="shared" si="6"/>
+        <v>81</v>
+      </c>
+      <c r="J154">
+        <v>256</v>
+      </c>
+      <c r="K154" s="2">
+        <f t="shared" si="7"/>
+        <v>316.40625</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155">
+        <v>180</v>
+      </c>
+      <c r="C155" s="1">
+        <v>9</v>
+      </c>
+      <c r="D155" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155">
+        <v>90</v>
+      </c>
+      <c r="F155" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="G155" t="s">
+        <v>7</v>
+      </c>
+      <c r="H155">
+        <v>388</v>
+      </c>
+      <c r="I155">
+        <f t="shared" si="6"/>
+        <v>85.5</v>
+      </c>
+      <c r="J155">
+        <v>256</v>
+      </c>
+      <c r="K155" s="2">
+        <f t="shared" si="7"/>
+        <v>333.984375</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156">
+        <v>180</v>
+      </c>
+      <c r="C156" s="1">
+        <v>9</v>
+      </c>
+      <c r="D156" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156">
+        <v>90</v>
+      </c>
+      <c r="F156" s="1">
+        <v>10</v>
+      </c>
+      <c r="G156" t="s">
+        <v>7</v>
+      </c>
+      <c r="H156">
+        <v>408</v>
+      </c>
+      <c r="I156">
+        <f t="shared" si="6"/>
+        <v>90</v>
+      </c>
+      <c r="J156">
+        <v>256</v>
+      </c>
+      <c r="K156" s="2">
+        <f t="shared" si="7"/>
+        <v>351.5625</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157">
+        <v>180</v>
+      </c>
+      <c r="C157" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D157" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157">
+        <v>90</v>
+      </c>
+      <c r="F157" s="1">
+        <v>1</v>
+      </c>
+      <c r="G157" t="s">
+        <v>7</v>
+      </c>
+      <c r="H157" s="1">
+        <v>71.8</v>
+      </c>
+      <c r="I157">
+        <f t="shared" si="6"/>
+        <v>15.8</v>
+      </c>
+      <c r="J157" s="1">
+        <v>455</v>
+      </c>
+      <c r="K157" s="2">
+        <f t="shared" si="7"/>
+        <v>34.725274725274723</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158">
+        <v>180</v>
+      </c>
+      <c r="C158" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D158" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158">
+        <v>90</v>
+      </c>
+      <c r="F158" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G158" t="s">
+        <v>7</v>
+      </c>
+      <c r="H158">
+        <v>108</v>
+      </c>
+      <c r="I158">
+        <f t="shared" si="6"/>
+        <v>23.700000000000003</v>
+      </c>
+      <c r="J158">
+        <v>455</v>
+      </c>
+      <c r="K158" s="2">
+        <f t="shared" si="7"/>
+        <v>52.087912087912095</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159">
+        <v>180</v>
+      </c>
+      <c r="C159" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D159" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159">
+        <v>90</v>
+      </c>
+      <c r="F159" s="1">
+        <v>2</v>
+      </c>
+      <c r="G159" t="s">
+        <v>7</v>
+      </c>
+      <c r="H159">
+        <v>144</v>
+      </c>
+      <c r="I159">
+        <f t="shared" si="6"/>
+        <v>31.6</v>
+      </c>
+      <c r="J159">
+        <v>455</v>
+      </c>
+      <c r="K159" s="2">
+        <f t="shared" si="7"/>
+        <v>69.450549450549445</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160">
+        <v>180</v>
+      </c>
+      <c r="C160" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D160" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160">
+        <v>90</v>
+      </c>
+      <c r="F160" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G160" t="s">
+        <v>7</v>
+      </c>
+      <c r="H160">
+        <v>180</v>
+      </c>
+      <c r="I160">
+        <f t="shared" si="6"/>
+        <v>39.5</v>
+      </c>
+      <c r="J160">
+        <v>455</v>
+      </c>
+      <c r="K160" s="2">
+        <f t="shared" si="7"/>
+        <v>86.813186813186817</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161">
+        <v>180</v>
+      </c>
+      <c r="C161" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D161" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161">
+        <v>90</v>
+      </c>
+      <c r="F161" s="1">
+        <v>3</v>
+      </c>
+      <c r="G161" t="s">
+        <v>7</v>
+      </c>
+      <c r="H161">
+        <v>216</v>
+      </c>
+      <c r="I161">
+        <f t="shared" si="6"/>
+        <v>47.400000000000006</v>
+      </c>
+      <c r="J161">
+        <v>455</v>
+      </c>
+      <c r="K161" s="2">
+        <f t="shared" si="7"/>
+        <v>104.17582417582419</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162">
+        <v>180</v>
+      </c>
+      <c r="C162" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D162" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162">
+        <v>90</v>
+      </c>
+      <c r="F162" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G162" t="s">
+        <v>7</v>
+      </c>
+      <c r="H162">
+        <v>252</v>
+      </c>
+      <c r="I162">
+        <f t="shared" si="6"/>
+        <v>55.300000000000004</v>
+      </c>
+      <c r="J162">
+        <v>455</v>
+      </c>
+      <c r="K162" s="2">
+        <f t="shared" si="7"/>
+        <v>121.53846153846156</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163">
+        <v>180</v>
+      </c>
+      <c r="C163" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D163" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163">
+        <v>90</v>
+      </c>
+      <c r="F163" s="1">
+        <v>4</v>
+      </c>
+      <c r="G163" t="s">
+        <v>7</v>
+      </c>
+      <c r="H163">
+        <v>287</v>
+      </c>
+      <c r="I163">
+        <f t="shared" si="6"/>
+        <v>63.2</v>
+      </c>
+      <c r="J163">
+        <v>455</v>
+      </c>
+      <c r="K163" s="2">
+        <f t="shared" si="7"/>
+        <v>138.90109890109889</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164">
+        <v>180</v>
+      </c>
+      <c r="C164" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D164" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164">
+        <v>90</v>
+      </c>
+      <c r="F164" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G164" t="s">
+        <v>7</v>
+      </c>
+      <c r="H164">
+        <v>323</v>
+      </c>
+      <c r="I164">
+        <f t="shared" si="6"/>
+        <v>71.100000000000009</v>
+      </c>
+      <c r="J164">
+        <v>455</v>
+      </c>
+      <c r="K164" s="2">
+        <f t="shared" si="7"/>
+        <v>156.26373626373629</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165">
+        <v>180</v>
+      </c>
+      <c r="C165" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D165" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165">
+        <v>90</v>
+      </c>
+      <c r="F165" s="1">
+        <v>5</v>
+      </c>
+      <c r="G165" t="s">
+        <v>7</v>
+      </c>
+      <c r="H165">
+        <v>359</v>
+      </c>
+      <c r="I165">
+        <f t="shared" si="6"/>
+        <v>79</v>
+      </c>
+      <c r="J165">
+        <v>455</v>
+      </c>
+      <c r="K165" s="2">
+        <f t="shared" si="7"/>
+        <v>173.62637362637363</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166">
+        <v>180</v>
+      </c>
+      <c r="C166" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D166" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166">
+        <v>90</v>
+      </c>
+      <c r="F166" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G166" t="s">
+        <v>7</v>
+      </c>
+      <c r="H166">
+        <v>395</v>
+      </c>
+      <c r="I166">
+        <f t="shared" si="6"/>
+        <v>86.9</v>
+      </c>
+      <c r="J166">
+        <v>455</v>
+      </c>
+      <c r="K166" s="2">
+        <f t="shared" si="7"/>
+        <v>190.98901098901098</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167">
+        <v>180</v>
+      </c>
+      <c r="C167" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D167" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167">
+        <v>90</v>
+      </c>
+      <c r="F167" s="1">
+        <v>6</v>
+      </c>
+      <c r="G167" t="s">
+        <v>7</v>
+      </c>
+      <c r="H167">
+        <v>431</v>
+      </c>
+      <c r="I167">
+        <f t="shared" si="6"/>
+        <v>94.800000000000011</v>
+      </c>
+      <c r="J167">
+        <v>455</v>
+      </c>
+      <c r="K167" s="2">
+        <f t="shared" si="7"/>
+        <v>208.35164835164838</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>8</v>
+      </c>
+      <c r="B168">
+        <v>180</v>
+      </c>
+      <c r="C168" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D168" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168">
+        <v>90</v>
+      </c>
+      <c r="F168" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G168" t="s">
+        <v>7</v>
+      </c>
+      <c r="H168">
+        <v>467</v>
+      </c>
+      <c r="I168">
+        <f t="shared" si="6"/>
+        <v>102.7</v>
+      </c>
+      <c r="J168">
+        <v>455</v>
+      </c>
+      <c r="K168" s="2">
+        <f t="shared" si="7"/>
+        <v>225.71428571428572</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169">
+        <v>180</v>
+      </c>
+      <c r="C169" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D169" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169">
+        <v>90</v>
+      </c>
+      <c r="F169" s="1">
+        <v>7</v>
+      </c>
+      <c r="G169" t="s">
+        <v>7</v>
+      </c>
+      <c r="H169">
+        <v>503</v>
+      </c>
+      <c r="I169">
+        <f t="shared" si="6"/>
+        <v>110.60000000000001</v>
+      </c>
+      <c r="J169">
+        <v>455</v>
+      </c>
+      <c r="K169" s="2">
+        <f t="shared" si="7"/>
+        <v>243.07692307692312</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170">
+        <v>180</v>
+      </c>
+      <c r="C170" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D170" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170">
+        <v>90</v>
+      </c>
+      <c r="F170" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G170" t="s">
+        <v>7</v>
+      </c>
+      <c r="H170">
+        <v>539</v>
+      </c>
+      <c r="I170">
+        <f t="shared" si="6"/>
+        <v>118.5</v>
+      </c>
+      <c r="J170">
+        <v>455</v>
+      </c>
+      <c r="K170" s="2">
+        <f t="shared" si="7"/>
+        <v>260.43956043956047</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171">
+        <v>180</v>
+      </c>
+      <c r="C171" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D171" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171">
+        <v>90</v>
+      </c>
+      <c r="F171" s="1">
+        <v>8</v>
+      </c>
+      <c r="G171" t="s">
+        <v>7</v>
+      </c>
+      <c r="H171">
+        <v>575</v>
+      </c>
+      <c r="I171">
+        <f t="shared" si="6"/>
+        <v>126.4</v>
+      </c>
+      <c r="J171">
+        <v>455</v>
+      </c>
+      <c r="K171" s="2">
+        <f t="shared" si="7"/>
+        <v>277.80219780219778</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172">
+        <v>180</v>
+      </c>
+      <c r="C172" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D172" t="s">
+        <v>12</v>
+      </c>
+      <c r="E172">
+        <v>90</v>
+      </c>
+      <c r="F172" s="1">
+        <v>1</v>
+      </c>
+      <c r="G172" t="s">
+        <v>7</v>
+      </c>
+      <c r="H172">
+        <v>71.8</v>
+      </c>
+      <c r="I172">
+        <f t="shared" si="6"/>
+        <v>15.8</v>
+      </c>
+      <c r="J172">
+        <v>309</v>
+      </c>
+      <c r="K172" s="2">
+        <f t="shared" si="7"/>
+        <v>51.132686084142392</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>8</v>
+      </c>
+      <c r="B173">
+        <v>180</v>
+      </c>
+      <c r="C173" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D173" t="s">
+        <v>12</v>
+      </c>
+      <c r="E173">
+        <v>90</v>
+      </c>
+      <c r="F173" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G173" t="s">
+        <v>7</v>
+      </c>
+      <c r="H173">
+        <v>108</v>
+      </c>
+      <c r="I173">
+        <f t="shared" si="6"/>
+        <v>23.700000000000003</v>
+      </c>
+      <c r="J173">
+        <v>309</v>
+      </c>
+      <c r="K173" s="2">
+        <f t="shared" si="7"/>
+        <v>76.699029126213603</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174">
+        <v>180</v>
+      </c>
+      <c r="C174" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D174" t="s">
+        <v>12</v>
+      </c>
+      <c r="E174">
+        <v>90</v>
+      </c>
+      <c r="F174" s="1">
+        <v>2</v>
+      </c>
+      <c r="G174" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174">
+        <v>144</v>
+      </c>
+      <c r="I174">
+        <f t="shared" si="6"/>
+        <v>31.6</v>
+      </c>
+      <c r="J174">
+        <v>309</v>
+      </c>
+      <c r="K174" s="2">
+        <f t="shared" si="7"/>
+        <v>102.26537216828478</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175">
+        <v>180</v>
+      </c>
+      <c r="C175" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D175" t="s">
+        <v>12</v>
+      </c>
+      <c r="E175">
+        <v>90</v>
+      </c>
+      <c r="F175" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G175" t="s">
+        <v>7</v>
+      </c>
+      <c r="H175">
+        <v>180</v>
+      </c>
+      <c r="I175">
+        <f t="shared" si="6"/>
+        <v>39.5</v>
+      </c>
+      <c r="J175">
+        <v>309</v>
+      </c>
+      <c r="K175" s="2">
+        <f t="shared" si="7"/>
+        <v>127.83171521035598</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>8</v>
+      </c>
+      <c r="B176">
+        <v>180</v>
+      </c>
+      <c r="C176" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D176" t="s">
+        <v>12</v>
+      </c>
+      <c r="E176">
+        <v>90</v>
+      </c>
+      <c r="F176" s="1">
+        <v>3</v>
+      </c>
+      <c r="G176" t="s">
+        <v>7</v>
+      </c>
+      <c r="H176">
+        <v>216</v>
+      </c>
+      <c r="I176">
+        <f t="shared" si="6"/>
+        <v>47.400000000000006</v>
+      </c>
+      <c r="J176">
+        <v>309</v>
+      </c>
+      <c r="K176" s="2">
+        <f t="shared" si="7"/>
+        <v>153.39805825242721</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177">
+        <v>180</v>
+      </c>
+      <c r="C177" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D177" t="s">
+        <v>12</v>
+      </c>
+      <c r="E177">
+        <v>90</v>
+      </c>
+      <c r="F177" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G177" t="s">
+        <v>7</v>
+      </c>
+      <c r="H177">
+        <v>252</v>
+      </c>
+      <c r="I177">
+        <f t="shared" si="6"/>
+        <v>55.300000000000004</v>
+      </c>
+      <c r="J177">
+        <v>309</v>
+      </c>
+      <c r="K177" s="2">
+        <f t="shared" si="7"/>
+        <v>178.9644012944984</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178">
+        <v>180</v>
+      </c>
+      <c r="C178" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D178" t="s">
+        <v>12</v>
+      </c>
+      <c r="E178">
+        <v>90</v>
+      </c>
+      <c r="F178" s="1">
+        <v>4</v>
+      </c>
+      <c r="G178" t="s">
+        <v>7</v>
+      </c>
+      <c r="H178">
+        <v>287</v>
+      </c>
+      <c r="I178">
+        <f t="shared" si="6"/>
+        <v>63.2</v>
+      </c>
+      <c r="J178">
+        <v>309</v>
+      </c>
+      <c r="K178" s="2">
+        <f t="shared" si="7"/>
+        <v>204.53074433656957</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179">
+        <v>180</v>
+      </c>
+      <c r="C179" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D179" t="s">
+        <v>12</v>
+      </c>
+      <c r="E179">
+        <v>90</v>
+      </c>
+      <c r="F179" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G179" t="s">
+        <v>7</v>
+      </c>
+      <c r="H179">
+        <v>323</v>
+      </c>
+      <c r="I179">
+        <f t="shared" si="6"/>
+        <v>71.100000000000009</v>
+      </c>
+      <c r="J179">
+        <v>309</v>
+      </c>
+      <c r="K179" s="2">
+        <f t="shared" si="7"/>
+        <v>230.09708737864082</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180">
+        <v>180</v>
+      </c>
+      <c r="C180" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D180" t="s">
+        <v>12</v>
+      </c>
+      <c r="E180">
+        <v>90</v>
+      </c>
+      <c r="F180" s="1">
+        <v>5</v>
+      </c>
+      <c r="G180" t="s">
+        <v>7</v>
+      </c>
+      <c r="H180">
+        <v>359</v>
+      </c>
+      <c r="I180">
+        <f t="shared" si="6"/>
+        <v>79</v>
+      </c>
+      <c r="J180">
+        <v>309</v>
+      </c>
+      <c r="K180" s="2">
+        <f t="shared" si="7"/>
+        <v>255.66343042071196</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181">
+        <v>180</v>
+      </c>
+      <c r="C181" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D181" t="s">
+        <v>12</v>
+      </c>
+      <c r="E181">
+        <v>90</v>
+      </c>
+      <c r="F181" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G181" t="s">
+        <v>7</v>
+      </c>
+      <c r="H181">
+        <v>395</v>
+      </c>
+      <c r="I181">
+        <f t="shared" si="6"/>
+        <v>86.9</v>
+      </c>
+      <c r="J181">
+        <v>309</v>
+      </c>
+      <c r="K181" s="2">
+        <f t="shared" si="7"/>
+        <v>281.22977346278316</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182">
+        <v>180</v>
+      </c>
+      <c r="C182" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D182" t="s">
+        <v>12</v>
+      </c>
+      <c r="E182">
+        <v>90</v>
+      </c>
+      <c r="F182" s="1">
+        <v>6</v>
+      </c>
+      <c r="G182" t="s">
+        <v>7</v>
+      </c>
+      <c r="H182">
+        <v>431</v>
+      </c>
+      <c r="I182">
+        <f t="shared" si="6"/>
+        <v>94.800000000000011</v>
+      </c>
+      <c r="J182">
+        <v>309</v>
+      </c>
+      <c r="K182" s="2">
+        <f t="shared" si="7"/>
+        <v>306.79611650485441</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>8</v>
+      </c>
+      <c r="B183">
+        <v>180</v>
+      </c>
+      <c r="C183" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D183" t="s">
+        <v>12</v>
+      </c>
+      <c r="E183">
+        <v>90</v>
+      </c>
+      <c r="F183" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G183" t="s">
+        <v>7</v>
+      </c>
+      <c r="H183">
+        <v>467</v>
+      </c>
+      <c r="I183">
+        <f t="shared" si="6"/>
+        <v>102.7</v>
+      </c>
+      <c r="J183">
+        <v>309</v>
+      </c>
+      <c r="K183" s="2">
+        <f t="shared" si="7"/>
+        <v>332.36245954692555</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>8</v>
+      </c>
+      <c r="B184">
+        <v>180</v>
+      </c>
+      <c r="C184" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D184" t="s">
+        <v>12</v>
+      </c>
+      <c r="E184">
+        <v>90</v>
+      </c>
+      <c r="F184" s="1">
+        <v>7</v>
+      </c>
+      <c r="G184" t="s">
+        <v>7</v>
+      </c>
+      <c r="H184">
+        <v>503</v>
+      </c>
+      <c r="I184">
+        <f t="shared" si="6"/>
+        <v>110.60000000000001</v>
+      </c>
+      <c r="J184">
+        <v>309</v>
+      </c>
+      <c r="K184" s="2">
+        <f t="shared" si="7"/>
+        <v>357.9288025889968</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185">
+        <v>180</v>
+      </c>
+      <c r="C185" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D185" t="s">
+        <v>12</v>
+      </c>
+      <c r="E185">
+        <v>90</v>
+      </c>
+      <c r="F185" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G185" t="s">
+        <v>7</v>
+      </c>
+      <c r="H185">
+        <v>539</v>
+      </c>
+      <c r="I185">
+        <f t="shared" si="6"/>
+        <v>118.5</v>
+      </c>
+      <c r="J185">
+        <v>309</v>
+      </c>
+      <c r="K185" s="2">
+        <f t="shared" si="7"/>
+        <v>383.49514563106794</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186">
+        <v>180</v>
+      </c>
+      <c r="C186" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D186" t="s">
+        <v>12</v>
+      </c>
+      <c r="E186">
+        <v>90</v>
+      </c>
+      <c r="F186" s="1">
+        <v>8</v>
+      </c>
+      <c r="G186" t="s">
+        <v>7</v>
+      </c>
+      <c r="H186">
+        <v>575</v>
+      </c>
+      <c r="I186">
+        <f t="shared" si="6"/>
+        <v>126.4</v>
+      </c>
+      <c r="J186">
+        <v>309</v>
+      </c>
+      <c r="K186" s="2">
+        <f t="shared" si="7"/>
+        <v>409.06148867313914</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187">
+        <v>180</v>
+      </c>
+      <c r="C187" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D187" t="s">
+        <v>13</v>
+      </c>
+      <c r="E187">
+        <v>90</v>
+      </c>
+      <c r="F187" s="1">
+        <v>1</v>
+      </c>
+      <c r="G187" t="s">
+        <v>7</v>
+      </c>
+      <c r="I187">
+        <f t="shared" si="6"/>
+        <v>5.4</v>
+      </c>
+      <c r="J187">
+        <v>270</v>
+      </c>
+      <c r="K187" s="2">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188">
+        <v>180</v>
+      </c>
+      <c r="C188" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D188" t="s">
+        <v>13</v>
+      </c>
+      <c r="E188">
+        <v>90</v>
+      </c>
+      <c r="F188" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G188" t="s">
+        <v>7</v>
+      </c>
+      <c r="I188">
+        <f t="shared" si="6"/>
+        <v>8.1000000000000014</v>
+      </c>
+      <c r="J188">
+        <v>270</v>
+      </c>
+      <c r="K188" s="2">
+        <f t="shared" si="7"/>
+        <v>30.000000000000007</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189">
+        <v>180</v>
+      </c>
+      <c r="C189" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D189" t="s">
+        <v>13</v>
+      </c>
+      <c r="E189">
+        <v>90</v>
+      </c>
+      <c r="F189" s="1">
+        <v>2</v>
+      </c>
+      <c r="G189" t="s">
+        <v>7</v>
+      </c>
+      <c r="I189">
+        <f t="shared" si="6"/>
+        <v>10.8</v>
+      </c>
+      <c r="J189">
+        <v>270</v>
+      </c>
+      <c r="K189" s="2">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190">
+        <v>180</v>
+      </c>
+      <c r="C190" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D190" t="s">
+        <v>13</v>
+      </c>
+      <c r="E190">
+        <v>90</v>
+      </c>
+      <c r="F190" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G190" t="s">
+        <v>7</v>
+      </c>
+      <c r="I190">
+        <f t="shared" si="6"/>
+        <v>13.5</v>
+      </c>
+      <c r="J190">
+        <v>270</v>
+      </c>
+      <c r="K190" s="2">
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191">
+        <v>180</v>
+      </c>
+      <c r="C191" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D191" t="s">
+        <v>13</v>
+      </c>
+      <c r="E191">
+        <v>90</v>
+      </c>
+      <c r="F191" s="1">
+        <v>3</v>
+      </c>
+      <c r="G191" t="s">
+        <v>7</v>
+      </c>
+      <c r="I191">
+        <f t="shared" si="6"/>
+        <v>16.200000000000003</v>
+      </c>
+      <c r="J191">
+        <v>270</v>
+      </c>
+      <c r="K191" s="2">
+        <f t="shared" si="7"/>
+        <v>60.000000000000014</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>8</v>
+      </c>
+      <c r="B192">
+        <v>180</v>
+      </c>
+      <c r="C192" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D192" t="s">
+        <v>13</v>
+      </c>
+      <c r="E192">
+        <v>90</v>
+      </c>
+      <c r="F192" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G192" t="s">
+        <v>7</v>
+      </c>
+      <c r="I192">
+        <f t="shared" si="6"/>
+        <v>18.900000000000002</v>
+      </c>
+      <c r="J192">
+        <v>270</v>
+      </c>
+      <c r="K192" s="2">
+        <f t="shared" si="7"/>
+        <v>70.000000000000014</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>8</v>
+      </c>
+      <c r="B193">
+        <v>180</v>
+      </c>
+      <c r="C193" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D193" t="s">
+        <v>13</v>
+      </c>
+      <c r="E193">
+        <v>90</v>
+      </c>
+      <c r="F193" s="1">
+        <v>4</v>
+      </c>
+      <c r="G193" t="s">
+        <v>7</v>
+      </c>
+      <c r="I193">
+        <f t="shared" si="6"/>
+        <v>21.6</v>
+      </c>
+      <c r="J193">
+        <v>270</v>
+      </c>
+      <c r="K193" s="2">
+        <f t="shared" si="7"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>8</v>
+      </c>
+      <c r="B194">
+        <v>180</v>
+      </c>
+      <c r="C194" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D194" t="s">
+        <v>13</v>
+      </c>
+      <c r="E194">
+        <v>90</v>
+      </c>
+      <c r="F194" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G194" t="s">
+        <v>7</v>
+      </c>
+      <c r="I194">
+        <f t="shared" si="6"/>
+        <v>24.3</v>
+      </c>
+      <c r="J194">
+        <v>270</v>
+      </c>
+      <c r="K194" s="2">
+        <f t="shared" si="7"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>8</v>
+      </c>
+      <c r="B195">
+        <v>180</v>
+      </c>
+      <c r="C195" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D195" t="s">
+        <v>13</v>
+      </c>
+      <c r="E195">
+        <v>90</v>
+      </c>
+      <c r="F195" s="1">
+        <v>5</v>
+      </c>
+      <c r="G195" t="s">
+        <v>7</v>
+      </c>
+      <c r="I195">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="J195">
+        <v>270</v>
+      </c>
+      <c r="K195" s="2">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>8</v>
+      </c>
+      <c r="B196">
+        <v>180</v>
+      </c>
+      <c r="C196" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D196" t="s">
+        <v>13</v>
+      </c>
+      <c r="E196">
+        <v>90</v>
+      </c>
+      <c r="F196" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G196" t="s">
+        <v>7</v>
+      </c>
+      <c r="I196">
+        <f t="shared" si="6"/>
+        <v>29.700000000000003</v>
+      </c>
+      <c r="J196">
+        <v>270</v>
+      </c>
+      <c r="K196" s="2">
+        <f t="shared" si="7"/>
+        <v>110.00000000000001</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>8</v>
+      </c>
+      <c r="B197">
+        <v>180</v>
+      </c>
+      <c r="C197" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>13</v>
+      </c>
+      <c r="E197">
+        <v>90</v>
+      </c>
+      <c r="F197" s="1">
+        <v>6</v>
+      </c>
+      <c r="G197" t="s">
+        <v>7</v>
+      </c>
+      <c r="I197">
+        <f t="shared" si="6"/>
+        <v>32.400000000000006</v>
+      </c>
+      <c r="J197">
+        <v>270</v>
+      </c>
+      <c r="K197" s="2">
+        <f t="shared" si="7"/>
+        <v>120.00000000000003</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>8</v>
+      </c>
+      <c r="B198">
+        <v>180</v>
+      </c>
+      <c r="C198" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D198" t="s">
+        <v>13</v>
+      </c>
+      <c r="E198">
+        <v>90</v>
+      </c>
+      <c r="F198" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G198" t="s">
+        <v>7</v>
+      </c>
+      <c r="I198">
+        <f t="shared" si="6"/>
+        <v>35.1</v>
+      </c>
+      <c r="J198">
+        <v>270</v>
+      </c>
+      <c r="K198" s="2">
+        <f t="shared" si="7"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>8</v>
+      </c>
+      <c r="B199">
+        <v>180</v>
+      </c>
+      <c r="C199" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D199" t="s">
+        <v>13</v>
+      </c>
+      <c r="E199">
+        <v>90</v>
+      </c>
+      <c r="F199" s="1">
+        <v>7</v>
+      </c>
+      <c r="G199" t="s">
+        <v>7</v>
+      </c>
+      <c r="I199">
+        <f t="shared" si="6"/>
+        <v>37.800000000000004</v>
+      </c>
+      <c r="J199">
+        <v>270</v>
+      </c>
+      <c r="K199" s="2">
+        <f t="shared" si="7"/>
+        <v>140.00000000000003</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>8</v>
+      </c>
+      <c r="B200">
+        <v>180</v>
+      </c>
+      <c r="C200" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D200" t="s">
+        <v>13</v>
+      </c>
+      <c r="E200">
+        <v>90</v>
+      </c>
+      <c r="F200" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G200" t="s">
+        <v>7</v>
+      </c>
+      <c r="I200">
+        <f t="shared" si="6"/>
+        <v>40.5</v>
+      </c>
+      <c r="J200">
+        <v>270</v>
+      </c>
+      <c r="K200" s="2">
+        <f t="shared" si="7"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>8</v>
+      </c>
+      <c r="B201">
+        <v>180</v>
+      </c>
+      <c r="C201" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D201" t="s">
+        <v>13</v>
+      </c>
+      <c r="E201">
+        <v>90</v>
+      </c>
+      <c r="F201" s="1">
+        <v>8</v>
+      </c>
+      <c r="G201" t="s">
+        <v>7</v>
+      </c>
+      <c r="I201">
+        <f t="shared" si="6"/>
+        <v>43.2</v>
+      </c>
+      <c r="J201">
+        <v>270</v>
+      </c>
+      <c r="K201" s="2">
+        <f t="shared" si="7"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>8</v>
+      </c>
+      <c r="B202">
+        <v>180</v>
+      </c>
+      <c r="C202" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D202" t="s">
+        <v>13</v>
+      </c>
+      <c r="E202">
+        <v>90</v>
+      </c>
+      <c r="F202" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G202" t="s">
+        <v>7</v>
+      </c>
+      <c r="I202">
+        <f t="shared" si="6"/>
+        <v>45.900000000000006</v>
+      </c>
+      <c r="J202">
+        <v>270</v>
+      </c>
+      <c r="K202" s="2">
+        <f t="shared" si="7"/>
+        <v>170.00000000000003</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>8</v>
+      </c>
+      <c r="B203">
+        <v>180</v>
+      </c>
+      <c r="C203" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D203" t="s">
+        <v>13</v>
+      </c>
+      <c r="E203">
+        <v>90</v>
+      </c>
+      <c r="F203" s="1">
+        <v>9</v>
+      </c>
+      <c r="G203" t="s">
+        <v>7</v>
+      </c>
+      <c r="I203">
+        <f t="shared" ref="I203:I266" si="8">C203*F203</f>
+        <v>48.6</v>
+      </c>
+      <c r="J203">
+        <v>270</v>
+      </c>
+      <c r="K203" s="2">
+        <f t="shared" ref="K203:K266" si="9">1000*I203/J203</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>8</v>
+      </c>
+      <c r="B204">
+        <v>180</v>
+      </c>
+      <c r="C204" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D204" t="s">
+        <v>13</v>
+      </c>
+      <c r="E204">
+        <v>90</v>
+      </c>
+      <c r="F204" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="G204" t="s">
+        <v>7</v>
+      </c>
+      <c r="I204">
+        <f t="shared" si="8"/>
+        <v>51.300000000000004</v>
+      </c>
+      <c r="J204">
+        <v>270</v>
+      </c>
+      <c r="K204" s="2">
+        <f t="shared" si="9"/>
+        <v>190.00000000000003</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>8</v>
+      </c>
+      <c r="B205">
+        <v>180</v>
+      </c>
+      <c r="C205" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D205" t="s">
+        <v>13</v>
+      </c>
+      <c r="E205">
+        <v>90</v>
+      </c>
+      <c r="F205" s="1">
+        <v>10</v>
+      </c>
+      <c r="G205" t="s">
+        <v>7</v>
+      </c>
+      <c r="I205">
+        <f t="shared" si="8"/>
+        <v>54</v>
+      </c>
+      <c r="J205">
+        <v>270</v>
+      </c>
+      <c r="K205" s="2">
+        <f t="shared" si="9"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>8</v>
+      </c>
+      <c r="B206">
+        <v>360</v>
+      </c>
+      <c r="C206" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D206" t="s">
+        <v>10</v>
+      </c>
+      <c r="E206">
+        <v>90</v>
+      </c>
+      <c r="F206" s="1">
+        <v>1</v>
+      </c>
+      <c r="G206" t="s">
+        <v>7</v>
+      </c>
+      <c r="I206">
+        <f t="shared" si="8"/>
+        <v>17.5</v>
+      </c>
+      <c r="J206">
+        <v>512</v>
+      </c>
+      <c r="K206" s="2">
+        <f t="shared" si="9"/>
+        <v>34.1796875</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>8</v>
+      </c>
+      <c r="B207">
+        <v>360</v>
+      </c>
+      <c r="C207" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D207" t="s">
+        <v>10</v>
+      </c>
+      <c r="E207">
+        <v>90</v>
+      </c>
+      <c r="F207" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G207" t="s">
+        <v>7</v>
+      </c>
+      <c r="I207">
+        <f t="shared" si="8"/>
+        <v>26.25</v>
+      </c>
+      <c r="J207">
+        <v>512</v>
+      </c>
+      <c r="K207" s="2">
+        <f t="shared" si="9"/>
+        <v>51.26953125</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>8</v>
+      </c>
+      <c r="B208">
+        <v>360</v>
+      </c>
+      <c r="C208" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D208" t="s">
+        <v>10</v>
+      </c>
+      <c r="E208">
+        <v>90</v>
+      </c>
+      <c r="F208" s="1">
+        <v>2</v>
+      </c>
+      <c r="G208" t="s">
+        <v>7</v>
+      </c>
+      <c r="I208">
+        <f t="shared" si="8"/>
+        <v>35</v>
+      </c>
+      <c r="J208">
+        <v>512</v>
+      </c>
+      <c r="K208" s="2">
+        <f t="shared" si="9"/>
+        <v>68.359375</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>8</v>
+      </c>
+      <c r="B209">
+        <v>360</v>
+      </c>
+      <c r="C209" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D209" t="s">
+        <v>10</v>
+      </c>
+      <c r="E209">
+        <v>90</v>
+      </c>
+      <c r="F209" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G209" t="s">
+        <v>7</v>
+      </c>
+      <c r="I209">
+        <f t="shared" si="8"/>
+        <v>43.75</v>
+      </c>
+      <c r="J209">
+        <v>512</v>
+      </c>
+      <c r="K209" s="2">
+        <f t="shared" si="9"/>
+        <v>85.44921875</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>8</v>
+      </c>
+      <c r="B210">
+        <v>360</v>
+      </c>
+      <c r="C210" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D210" t="s">
+        <v>10</v>
+      </c>
+      <c r="E210">
+        <v>90</v>
+      </c>
+      <c r="F210" s="1">
+        <v>3</v>
+      </c>
+      <c r="G210" t="s">
+        <v>7</v>
+      </c>
+      <c r="I210">
+        <f t="shared" si="8"/>
+        <v>52.5</v>
+      </c>
+      <c r="J210">
+        <v>512</v>
+      </c>
+      <c r="K210" s="2">
+        <f t="shared" si="9"/>
+        <v>102.5390625</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>8</v>
+      </c>
+      <c r="B211">
+        <v>360</v>
+      </c>
+      <c r="C211" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D211" t="s">
+        <v>10</v>
+      </c>
+      <c r="E211">
+        <v>90</v>
+      </c>
+      <c r="F211" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G211" t="s">
+        <v>7</v>
+      </c>
+      <c r="I211">
+        <f t="shared" si="8"/>
+        <v>61.25</v>
+      </c>
+      <c r="J211">
+        <v>512</v>
+      </c>
+      <c r="K211" s="2">
+        <f t="shared" si="9"/>
+        <v>119.62890625</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212">
+        <v>360</v>
+      </c>
+      <c r="C212" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D212" t="s">
+        <v>10</v>
+      </c>
+      <c r="E212">
+        <v>90</v>
+      </c>
+      <c r="F212" s="1">
+        <v>4</v>
+      </c>
+      <c r="G212" t="s">
+        <v>7</v>
+      </c>
+      <c r="I212">
+        <f t="shared" si="8"/>
+        <v>70</v>
+      </c>
+      <c r="J212">
+        <v>512</v>
+      </c>
+      <c r="K212" s="2">
+        <f t="shared" si="9"/>
+        <v>136.71875</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>8</v>
+      </c>
+      <c r="B213">
+        <v>360</v>
+      </c>
+      <c r="C213" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D213" t="s">
+        <v>10</v>
+      </c>
+      <c r="E213">
+        <v>90</v>
+      </c>
+      <c r="F213" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G213" t="s">
+        <v>7</v>
+      </c>
+      <c r="I213">
+        <f t="shared" si="8"/>
+        <v>78.75</v>
+      </c>
+      <c r="J213">
+        <v>512</v>
+      </c>
+      <c r="K213" s="2">
+        <f t="shared" si="9"/>
+        <v>153.80859375</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>8</v>
+      </c>
+      <c r="B214">
+        <v>360</v>
+      </c>
+      <c r="C214" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D214" t="s">
+        <v>10</v>
+      </c>
+      <c r="E214">
+        <v>90</v>
+      </c>
+      <c r="F214" s="1">
+        <v>5</v>
+      </c>
+      <c r="G214" t="s">
+        <v>7</v>
+      </c>
+      <c r="I214">
+        <f t="shared" si="8"/>
+        <v>87.5</v>
+      </c>
+      <c r="J214">
+        <v>512</v>
+      </c>
+      <c r="K214" s="2">
+        <f t="shared" si="9"/>
+        <v>170.8984375</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>8</v>
+      </c>
+      <c r="B215">
+        <v>360</v>
+      </c>
+      <c r="C215" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D215" t="s">
+        <v>10</v>
+      </c>
+      <c r="E215">
+        <v>90</v>
+      </c>
+      <c r="F215" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G215" t="s">
+        <v>7</v>
+      </c>
+      <c r="I215">
+        <f t="shared" si="8"/>
+        <v>96.25</v>
+      </c>
+      <c r="J215">
+        <v>512</v>
+      </c>
+      <c r="K215" s="2">
+        <f t="shared" si="9"/>
+        <v>187.98828125</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>8</v>
+      </c>
+      <c r="B216">
+        <v>360</v>
+      </c>
+      <c r="C216" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D216" t="s">
+        <v>10</v>
+      </c>
+      <c r="E216">
+        <v>90</v>
+      </c>
+      <c r="F216" s="1">
+        <v>6</v>
+      </c>
+      <c r="G216" t="s">
+        <v>7</v>
+      </c>
+      <c r="I216">
+        <f t="shared" si="8"/>
+        <v>105</v>
+      </c>
+      <c r="J216">
+        <v>512</v>
+      </c>
+      <c r="K216" s="2">
+        <f t="shared" si="9"/>
+        <v>205.078125</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>8</v>
+      </c>
+      <c r="B217">
+        <v>360</v>
+      </c>
+      <c r="C217" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D217" t="s">
+        <v>10</v>
+      </c>
+      <c r="E217">
+        <v>90</v>
+      </c>
+      <c r="F217" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G217" t="s">
+        <v>7</v>
+      </c>
+      <c r="I217">
+        <f t="shared" si="8"/>
+        <v>113.75</v>
+      </c>
+      <c r="J217">
+        <v>512</v>
+      </c>
+      <c r="K217" s="2">
+        <f t="shared" si="9"/>
+        <v>222.16796875</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>8</v>
+      </c>
+      <c r="B218">
+        <v>360</v>
+      </c>
+      <c r="C218" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>10</v>
+      </c>
+      <c r="E218">
+        <v>90</v>
+      </c>
+      <c r="F218" s="1">
+        <v>7</v>
+      </c>
+      <c r="G218" t="s">
+        <v>7</v>
+      </c>
+      <c r="I218">
+        <f t="shared" si="8"/>
+        <v>122.5</v>
+      </c>
+      <c r="J218">
+        <v>512</v>
+      </c>
+      <c r="K218" s="2">
+        <f t="shared" si="9"/>
+        <v>239.2578125</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>8</v>
+      </c>
+      <c r="B219">
+        <v>360</v>
+      </c>
+      <c r="C219" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D219" t="s">
+        <v>10</v>
+      </c>
+      <c r="E219">
+        <v>90</v>
+      </c>
+      <c r="F219" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G219" t="s">
+        <v>7</v>
+      </c>
+      <c r="I219">
+        <f t="shared" si="8"/>
+        <v>131.25</v>
+      </c>
+      <c r="J219">
+        <v>512</v>
+      </c>
+      <c r="K219" s="2">
+        <f t="shared" si="9"/>
+        <v>256.34765625</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>8</v>
+      </c>
+      <c r="B220">
+        <v>360</v>
+      </c>
+      <c r="C220" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D220" t="s">
+        <v>10</v>
+      </c>
+      <c r="E220">
+        <v>90</v>
+      </c>
+      <c r="F220" s="1">
+        <v>8</v>
+      </c>
+      <c r="G220" t="s">
+        <v>7</v>
+      </c>
+      <c r="I220">
+        <f t="shared" si="8"/>
+        <v>140</v>
+      </c>
+      <c r="J220">
+        <v>512</v>
+      </c>
+      <c r="K220" s="2">
+        <f t="shared" si="9"/>
+        <v>273.4375</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>8</v>
+      </c>
+      <c r="B221">
+        <v>360</v>
+      </c>
+      <c r="C221" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D221" t="s">
+        <v>10</v>
+      </c>
+      <c r="E221">
+        <v>90</v>
+      </c>
+      <c r="F221" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G221" t="s">
+        <v>7</v>
+      </c>
+      <c r="I221">
+        <f t="shared" si="8"/>
+        <v>148.75</v>
+      </c>
+      <c r="J221">
+        <v>512</v>
+      </c>
+      <c r="K221" s="2">
+        <f t="shared" si="9"/>
+        <v>290.52734375</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>8</v>
+      </c>
+      <c r="B222">
+        <v>360</v>
+      </c>
+      <c r="C222" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D222" t="s">
+        <v>10</v>
+      </c>
+      <c r="E222">
+        <v>90</v>
+      </c>
+      <c r="F222" s="1">
+        <v>9</v>
+      </c>
+      <c r="G222" t="s">
+        <v>7</v>
+      </c>
+      <c r="I222">
+        <f t="shared" si="8"/>
+        <v>157.5</v>
+      </c>
+      <c r="J222">
+        <v>512</v>
+      </c>
+      <c r="K222" s="2">
+        <f t="shared" si="9"/>
+        <v>307.6171875</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>8</v>
+      </c>
+      <c r="B223">
+        <v>360</v>
+      </c>
+      <c r="C223" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D223" t="s">
+        <v>10</v>
+      </c>
+      <c r="E223">
+        <v>90</v>
+      </c>
+      <c r="F223" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="G223" t="s">
+        <v>7</v>
+      </c>
+      <c r="I223">
+        <f t="shared" si="8"/>
+        <v>166.25</v>
+      </c>
+      <c r="J223">
+        <v>512</v>
+      </c>
+      <c r="K223" s="2">
+        <f t="shared" si="9"/>
+        <v>324.70703125</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>8</v>
+      </c>
+      <c r="B224">
+        <v>360</v>
+      </c>
+      <c r="C224" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="D224" t="s">
+        <v>10</v>
+      </c>
+      <c r="E224">
+        <v>90</v>
+      </c>
+      <c r="F224" s="1">
+        <v>10</v>
+      </c>
+      <c r="G224" t="s">
+        <v>7</v>
+      </c>
+      <c r="I224">
+        <f t="shared" si="8"/>
+        <v>175</v>
+      </c>
+      <c r="J224">
+        <v>512</v>
+      </c>
+      <c r="K224" s="2">
+        <f t="shared" si="9"/>
+        <v>341.796875</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>8</v>
+      </c>
+      <c r="B225">
+        <v>360</v>
+      </c>
+      <c r="C225" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D225" t="s">
+        <v>11</v>
+      </c>
+      <c r="E225">
+        <v>90</v>
+      </c>
+      <c r="F225" s="1">
+        <v>1</v>
+      </c>
+      <c r="G225" t="s">
+        <v>7</v>
+      </c>
+      <c r="H225">
+        <v>140</v>
+      </c>
+      <c r="I225">
+        <f t="shared" si="8"/>
+        <v>30.8</v>
+      </c>
+      <c r="J225">
+        <v>911</v>
+      </c>
+      <c r="K225" s="2">
+        <f t="shared" si="9"/>
+        <v>33.809001097694839</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>8</v>
+      </c>
+      <c r="B226">
+        <v>360</v>
+      </c>
+      <c r="C226" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D226" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226">
+        <v>90</v>
+      </c>
+      <c r="F226" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G226" t="s">
+        <v>7</v>
+      </c>
+      <c r="H226">
+        <v>210</v>
+      </c>
+      <c r="I226">
+        <f t="shared" si="8"/>
+        <v>46.2</v>
+      </c>
+      <c r="J226">
+        <v>911</v>
+      </c>
+      <c r="K226" s="2">
+        <f t="shared" si="9"/>
+        <v>50.713501646542262</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>8</v>
+      </c>
+      <c r="B227">
+        <v>360</v>
+      </c>
+      <c r="C227" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D227" t="s">
+        <v>11</v>
+      </c>
+      <c r="E227">
+        <v>90</v>
+      </c>
+      <c r="F227" s="1">
+        <v>2</v>
+      </c>
+      <c r="G227" t="s">
+        <v>7</v>
+      </c>
+      <c r="H227">
+        <v>280</v>
+      </c>
+      <c r="I227">
+        <f t="shared" si="8"/>
+        <v>61.6</v>
+      </c>
+      <c r="J227">
+        <v>911</v>
+      </c>
+      <c r="K227" s="2">
+        <f t="shared" si="9"/>
+        <v>67.618002195389678</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>8</v>
+      </c>
+      <c r="B228">
+        <v>360</v>
+      </c>
+      <c r="C228" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D228" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228">
+        <v>90</v>
+      </c>
+      <c r="F228" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G228" t="s">
+        <v>7</v>
+      </c>
+      <c r="H228">
+        <v>349</v>
+      </c>
+      <c r="I228">
+        <f t="shared" si="8"/>
+        <v>77</v>
+      </c>
+      <c r="J228">
+        <v>911</v>
+      </c>
+      <c r="K228" s="2">
+        <f t="shared" si="9"/>
+        <v>84.522502744237102</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>8</v>
+      </c>
+      <c r="B229">
+        <v>360</v>
+      </c>
+      <c r="C229" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D229" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229">
+        <v>90</v>
+      </c>
+      <c r="F229" s="1">
+        <v>3</v>
+      </c>
+      <c r="G229" t="s">
+        <v>7</v>
+      </c>
+      <c r="H229">
+        <v>419</v>
+      </c>
+      <c r="I229">
+        <f t="shared" si="8"/>
+        <v>92.4</v>
+      </c>
+      <c r="J229">
+        <v>911</v>
+      </c>
+      <c r="K229" s="2">
+        <f t="shared" si="9"/>
+        <v>101.42700329308452</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>8</v>
+      </c>
+      <c r="B230">
+        <v>360</v>
+      </c>
+      <c r="C230" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D230" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230">
+        <v>90</v>
+      </c>
+      <c r="F230" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G230" t="s">
+        <v>7</v>
+      </c>
+      <c r="H230">
+        <v>489</v>
+      </c>
+      <c r="I230">
+        <f t="shared" si="8"/>
+        <v>107.8</v>
+      </c>
+      <c r="J230">
+        <v>911</v>
+      </c>
+      <c r="K230" s="2">
+        <f t="shared" si="9"/>
+        <v>118.33150384193195</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>8</v>
+      </c>
+      <c r="B231">
+        <v>360</v>
+      </c>
+      <c r="C231" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D231" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231">
+        <v>90</v>
+      </c>
+      <c r="F231" s="1">
+        <v>4</v>
+      </c>
+      <c r="G231" t="s">
+        <v>7</v>
+      </c>
+      <c r="H231">
+        <v>559</v>
+      </c>
+      <c r="I231">
+        <f t="shared" si="8"/>
+        <v>123.2</v>
+      </c>
+      <c r="J231">
+        <v>911</v>
+      </c>
+      <c r="K231" s="2">
+        <f t="shared" si="9"/>
+        <v>135.23600439077936</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>8</v>
+      </c>
+      <c r="B232">
+        <v>360</v>
+      </c>
+      <c r="C232" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D232" t="s">
+        <v>11</v>
+      </c>
+      <c r="E232">
+        <v>90</v>
+      </c>
+      <c r="F232" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G232" t="s">
+        <v>7</v>
+      </c>
+      <c r="H232">
+        <v>629</v>
+      </c>
+      <c r="I232">
+        <f t="shared" si="8"/>
+        <v>138.6</v>
+      </c>
+      <c r="J232">
+        <v>911</v>
+      </c>
+      <c r="K232" s="2">
+        <f t="shared" si="9"/>
+        <v>152.14050493962679</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>8</v>
+      </c>
+      <c r="B233">
+        <v>360</v>
+      </c>
+      <c r="C233" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D233" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233">
+        <v>90</v>
+      </c>
+      <c r="F233" s="1">
+        <v>5</v>
+      </c>
+      <c r="G233" t="s">
+        <v>7</v>
+      </c>
+      <c r="H233">
+        <v>699</v>
+      </c>
+      <c r="I233">
+        <f t="shared" si="8"/>
+        <v>154</v>
+      </c>
+      <c r="J233">
+        <v>911</v>
+      </c>
+      <c r="K233" s="2">
+        <f t="shared" si="9"/>
+        <v>169.0450054884742</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>8</v>
+      </c>
+      <c r="B234">
+        <v>360</v>
+      </c>
+      <c r="C234" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D234" t="s">
+        <v>11</v>
+      </c>
+      <c r="E234">
+        <v>90</v>
+      </c>
+      <c r="F234" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G234" t="s">
+        <v>7</v>
+      </c>
+      <c r="H234">
+        <v>769</v>
+      </c>
+      <c r="I234">
+        <f t="shared" si="8"/>
+        <v>169.4</v>
+      </c>
+      <c r="J234">
+        <v>911</v>
+      </c>
+      <c r="K234" s="2">
+        <f t="shared" si="9"/>
+        <v>185.94950603732161</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>8</v>
+      </c>
+      <c r="B235">
+        <v>360</v>
+      </c>
+      <c r="C235" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D235" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235">
+        <v>90</v>
+      </c>
+      <c r="F235" s="1">
+        <v>6</v>
+      </c>
+      <c r="G235" t="s">
+        <v>7</v>
+      </c>
+      <c r="H235">
+        <v>839</v>
+      </c>
+      <c r="I235">
+        <f t="shared" si="8"/>
+        <v>184.8</v>
+      </c>
+      <c r="J235">
+        <v>911</v>
+      </c>
+      <c r="K235" s="2">
+        <f t="shared" si="9"/>
+        <v>202.85400658616905</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>8</v>
+      </c>
+      <c r="B236">
+        <v>360</v>
+      </c>
+      <c r="C236" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D236" t="s">
+        <v>11</v>
+      </c>
+      <c r="E236">
+        <v>90</v>
+      </c>
+      <c r="F236" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G236" t="s">
+        <v>7</v>
+      </c>
+      <c r="H236">
+        <v>908</v>
+      </c>
+      <c r="I236">
+        <f t="shared" si="8"/>
+        <v>200.20000000000002</v>
+      </c>
+      <c r="J236">
+        <v>911</v>
+      </c>
+      <c r="K236" s="2">
+        <f t="shared" si="9"/>
+        <v>219.75850713501649</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>8</v>
+      </c>
+      <c r="B237">
+        <v>360</v>
+      </c>
+      <c r="C237" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D237" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237">
+        <v>90</v>
+      </c>
+      <c r="F237" s="1">
+        <v>7</v>
+      </c>
+      <c r="G237" t="s">
+        <v>7</v>
+      </c>
+      <c r="H237">
+        <v>978</v>
+      </c>
+      <c r="I237">
+        <f t="shared" si="8"/>
+        <v>215.6</v>
+      </c>
+      <c r="J237">
+        <v>911</v>
+      </c>
+      <c r="K237" s="2">
+        <f t="shared" si="9"/>
+        <v>236.6630076838639</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>8</v>
+      </c>
+      <c r="B238">
+        <v>360</v>
+      </c>
+      <c r="C238" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D238" t="s">
+        <v>11</v>
+      </c>
+      <c r="E238">
+        <v>90</v>
+      </c>
+      <c r="F238" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G238" t="s">
+        <v>7</v>
+      </c>
+      <c r="H238">
+        <v>1050</v>
+      </c>
+      <c r="I238">
+        <f t="shared" si="8"/>
+        <v>231</v>
+      </c>
+      <c r="J238">
+        <v>911</v>
+      </c>
+      <c r="K238" s="2">
+        <f t="shared" si="9"/>
+        <v>253.5675082327113</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>8</v>
+      </c>
+      <c r="B239">
+        <v>360</v>
+      </c>
+      <c r="C239" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D239" t="s">
+        <v>11</v>
+      </c>
+      <c r="E239">
+        <v>90</v>
+      </c>
+      <c r="F239" s="1">
+        <v>8</v>
+      </c>
+      <c r="G239" t="s">
+        <v>7</v>
+      </c>
+      <c r="H239">
+        <v>1120</v>
+      </c>
+      <c r="I239">
+        <f t="shared" si="8"/>
+        <v>246.4</v>
+      </c>
+      <c r="J239">
+        <v>911</v>
+      </c>
+      <c r="K239" s="2">
+        <f t="shared" si="9"/>
+        <v>270.47200878155871</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>8</v>
+      </c>
+      <c r="B240">
+        <v>360</v>
+      </c>
+      <c r="C240" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D240" t="s">
+        <v>12</v>
+      </c>
+      <c r="E240">
+        <v>90</v>
+      </c>
+      <c r="F240" s="1">
+        <v>1</v>
+      </c>
+      <c r="G240" t="s">
+        <v>7</v>
+      </c>
+      <c r="H240">
+        <v>140</v>
+      </c>
+      <c r="I240">
+        <f t="shared" si="8"/>
+        <v>30.8</v>
+      </c>
+      <c r="J240">
+        <v>618</v>
+      </c>
+      <c r="K240" s="2">
+        <f t="shared" si="9"/>
+        <v>49.838187702265373</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>8</v>
+      </c>
+      <c r="B241">
+        <v>360</v>
+      </c>
+      <c r="C241" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D241" t="s">
+        <v>12</v>
+      </c>
+      <c r="E241">
+        <v>90</v>
+      </c>
+      <c r="F241" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G241" t="s">
+        <v>7</v>
+      </c>
+      <c r="H241">
+        <v>210</v>
+      </c>
+      <c r="I241">
+        <f t="shared" si="8"/>
+        <v>46.2</v>
+      </c>
+      <c r="J241">
+        <v>618</v>
+      </c>
+      <c r="K241" s="2">
+        <f t="shared" si="9"/>
+        <v>74.757281553398059</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>8</v>
+      </c>
+      <c r="B242">
+        <v>360</v>
+      </c>
+      <c r="C242" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D242" t="s">
+        <v>12</v>
+      </c>
+      <c r="E242">
+        <v>90</v>
+      </c>
+      <c r="F242" s="1">
+        <v>2</v>
+      </c>
+      <c r="G242" t="s">
+        <v>7</v>
+      </c>
+      <c r="H242">
+        <v>280</v>
+      </c>
+      <c r="I242">
+        <f t="shared" si="8"/>
+        <v>61.6</v>
+      </c>
+      <c r="J242">
+        <v>618</v>
+      </c>
+      <c r="K242" s="2">
+        <f t="shared" si="9"/>
+        <v>99.676375404530745</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>8</v>
+      </c>
+      <c r="B243">
+        <v>360</v>
+      </c>
+      <c r="C243" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D243" t="s">
+        <v>12</v>
+      </c>
+      <c r="E243">
+        <v>90</v>
+      </c>
+      <c r="F243" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G243" t="s">
+        <v>7</v>
+      </c>
+      <c r="H243">
+        <v>349</v>
+      </c>
+      <c r="I243">
+        <f t="shared" si="8"/>
+        <v>77</v>
+      </c>
+      <c r="J243">
+        <v>618</v>
+      </c>
+      <c r="K243" s="2">
+        <f t="shared" si="9"/>
+        <v>124.59546925566343</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>8</v>
+      </c>
+      <c r="B244">
+        <v>360</v>
+      </c>
+      <c r="C244" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D244" t="s">
+        <v>12</v>
+      </c>
+      <c r="E244">
+        <v>90</v>
+      </c>
+      <c r="F244" s="1">
+        <v>3</v>
+      </c>
+      <c r="G244" t="s">
+        <v>7</v>
+      </c>
+      <c r="H244">
+        <v>419</v>
+      </c>
+      <c r="I244">
+        <f t="shared" si="8"/>
+        <v>92.4</v>
+      </c>
+      <c r="J244">
+        <v>618</v>
+      </c>
+      <c r="K244" s="2">
+        <f t="shared" si="9"/>
+        <v>149.51456310679612</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>8</v>
+      </c>
+      <c r="B245">
+        <v>360</v>
+      </c>
+      <c r="C245" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D245" t="s">
+        <v>12</v>
+      </c>
+      <c r="E245">
+        <v>90</v>
+      </c>
+      <c r="F245" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G245" t="s">
+        <v>7</v>
+      </c>
+      <c r="H245">
+        <v>489</v>
+      </c>
+      <c r="I245">
+        <f t="shared" si="8"/>
+        <v>107.8</v>
+      </c>
+      <c r="J245">
+        <v>618</v>
+      </c>
+      <c r="K245" s="2">
+        <f t="shared" si="9"/>
+        <v>174.4336569579288</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>8</v>
+      </c>
+      <c r="B246">
+        <v>360</v>
+      </c>
+      <c r="C246" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D246" t="s">
+        <v>12</v>
+      </c>
+      <c r="E246">
+        <v>90</v>
+      </c>
+      <c r="F246" s="1">
+        <v>4</v>
+      </c>
+      <c r="G246" t="s">
+        <v>7</v>
+      </c>
+      <c r="H246">
+        <v>559</v>
+      </c>
+      <c r="I246">
+        <f t="shared" si="8"/>
+        <v>123.2</v>
+      </c>
+      <c r="J246">
+        <v>618</v>
+      </c>
+      <c r="K246" s="2">
+        <f t="shared" si="9"/>
+        <v>199.35275080906149</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>8</v>
+      </c>
+      <c r="B247">
+        <v>360</v>
+      </c>
+      <c r="C247" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D247" t="s">
+        <v>12</v>
+      </c>
+      <c r="E247">
+        <v>90</v>
+      </c>
+      <c r="F247" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G247" t="s">
+        <v>7</v>
+      </c>
+      <c r="H247">
+        <v>629</v>
+      </c>
+      <c r="I247">
+        <f t="shared" si="8"/>
+        <v>138.6</v>
+      </c>
+      <c r="J247">
+        <v>618</v>
+      </c>
+      <c r="K247" s="2">
+        <f t="shared" si="9"/>
+        <v>224.27184466019418</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>8</v>
+      </c>
+      <c r="B248">
+        <v>360</v>
+      </c>
+      <c r="C248" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D248" t="s">
+        <v>12</v>
+      </c>
+      <c r="E248">
+        <v>90</v>
+      </c>
+      <c r="F248" s="1">
+        <v>5</v>
+      </c>
+      <c r="G248" t="s">
+        <v>7</v>
+      </c>
+      <c r="H248">
+        <v>699</v>
+      </c>
+      <c r="I248">
+        <f t="shared" si="8"/>
+        <v>154</v>
+      </c>
+      <c r="J248">
+        <v>618</v>
+      </c>
+      <c r="K248" s="2">
+        <f t="shared" si="9"/>
+        <v>249.19093851132686</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>8</v>
+      </c>
+      <c r="B249">
+        <v>360</v>
+      </c>
+      <c r="C249" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D249" t="s">
+        <v>12</v>
+      </c>
+      <c r="E249">
+        <v>90</v>
+      </c>
+      <c r="F249" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G249" t="s">
+        <v>7</v>
+      </c>
+      <c r="H249">
+        <v>769</v>
+      </c>
+      <c r="I249">
+        <f t="shared" si="8"/>
+        <v>169.4</v>
+      </c>
+      <c r="J249">
+        <v>618</v>
+      </c>
+      <c r="K249" s="2">
+        <f t="shared" si="9"/>
+        <v>274.11003236245955</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>8</v>
+      </c>
+      <c r="B250">
+        <v>360</v>
+      </c>
+      <c r="C250" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D250" t="s">
+        <v>12</v>
+      </c>
+      <c r="E250">
+        <v>90</v>
+      </c>
+      <c r="F250" s="1">
+        <v>6</v>
+      </c>
+      <c r="G250" t="s">
+        <v>7</v>
+      </c>
+      <c r="H250">
+        <v>839</v>
+      </c>
+      <c r="I250">
+        <f t="shared" si="8"/>
+        <v>184.8</v>
+      </c>
+      <c r="J250">
+        <v>618</v>
+      </c>
+      <c r="K250" s="2">
+        <f t="shared" si="9"/>
+        <v>299.02912621359224</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>8</v>
+      </c>
+      <c r="B251">
+        <v>360</v>
+      </c>
+      <c r="C251" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D251" t="s">
+        <v>12</v>
+      </c>
+      <c r="E251">
+        <v>90</v>
+      </c>
+      <c r="F251" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G251" t="s">
+        <v>7</v>
+      </c>
+      <c r="H251">
+        <v>908</v>
+      </c>
+      <c r="I251">
+        <f t="shared" si="8"/>
+        <v>200.20000000000002</v>
+      </c>
+      <c r="J251">
+        <v>618</v>
+      </c>
+      <c r="K251" s="2">
+        <f t="shared" si="9"/>
+        <v>323.94822006472498</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>8</v>
+      </c>
+      <c r="B252">
+        <v>360</v>
+      </c>
+      <c r="C252" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D252" t="s">
+        <v>12</v>
+      </c>
+      <c r="E252">
+        <v>90</v>
+      </c>
+      <c r="F252" s="1">
+        <v>7</v>
+      </c>
+      <c r="G252" t="s">
+        <v>7</v>
+      </c>
+      <c r="H252">
+        <v>978</v>
+      </c>
+      <c r="I252">
+        <f t="shared" si="8"/>
+        <v>215.6</v>
+      </c>
+      <c r="J252">
+        <v>618</v>
+      </c>
+      <c r="K252" s="2">
+        <f t="shared" si="9"/>
+        <v>348.86731391585761</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>8</v>
+      </c>
+      <c r="B253">
+        <v>360</v>
+      </c>
+      <c r="C253" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D253" t="s">
+        <v>12</v>
+      </c>
+      <c r="E253">
+        <v>90</v>
+      </c>
+      <c r="F253" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G253" t="s">
+        <v>7</v>
+      </c>
+      <c r="H253">
+        <v>1050</v>
+      </c>
+      <c r="I253">
+        <f t="shared" si="8"/>
+        <v>231</v>
+      </c>
+      <c r="J253">
+        <v>618</v>
+      </c>
+      <c r="K253" s="2">
+        <f t="shared" si="9"/>
+        <v>373.78640776699029</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>8</v>
+      </c>
+      <c r="B254">
+        <v>360</v>
+      </c>
+      <c r="C254" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="D254" t="s">
+        <v>12</v>
+      </c>
+      <c r="E254">
+        <v>90</v>
+      </c>
+      <c r="F254" s="1">
+        <v>8</v>
+      </c>
+      <c r="G254" t="s">
+        <v>7</v>
+      </c>
+      <c r="H254">
+        <v>1120</v>
+      </c>
+      <c r="I254">
+        <f t="shared" si="8"/>
+        <v>246.4</v>
+      </c>
+      <c r="J254">
+        <v>618</v>
+      </c>
+      <c r="K254" s="2">
+        <f t="shared" si="9"/>
+        <v>398.70550161812298</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>8</v>
+      </c>
+      <c r="B255">
+        <v>360</v>
+      </c>
+      <c r="C255" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D255" t="s">
+        <v>13</v>
+      </c>
+      <c r="E255">
+        <v>90</v>
+      </c>
+      <c r="F255" s="1">
+        <v>1</v>
+      </c>
+      <c r="G255" t="s">
+        <v>7</v>
+      </c>
+      <c r="H255">
+        <v>47.6</v>
+      </c>
+      <c r="I255">
+        <f t="shared" si="8"/>
+        <v>10.5</v>
+      </c>
+      <c r="J255">
+        <v>540</v>
+      </c>
+      <c r="K255" s="2">
+        <f t="shared" si="9"/>
+        <v>19.444444444444443</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>8</v>
+      </c>
+      <c r="B256">
+        <v>360</v>
+      </c>
+      <c r="C256" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D256" t="s">
+        <v>13</v>
+      </c>
+      <c r="E256">
+        <v>90</v>
+      </c>
+      <c r="F256" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G256" t="s">
+        <v>7</v>
+      </c>
+      <c r="H256">
+        <v>71.5</v>
+      </c>
+      <c r="I256">
+        <f t="shared" si="8"/>
+        <v>15.75</v>
+      </c>
+      <c r="J256">
+        <v>540</v>
+      </c>
+      <c r="K256" s="2">
+        <f t="shared" si="9"/>
+        <v>29.166666666666668</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>8</v>
+      </c>
+      <c r="B257">
+        <v>360</v>
+      </c>
+      <c r="C257" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D257" t="s">
+        <v>13</v>
+      </c>
+      <c r="E257">
+        <v>90</v>
+      </c>
+      <c r="F257" s="1">
+        <v>2</v>
+      </c>
+      <c r="G257" t="s">
+        <v>7</v>
+      </c>
+      <c r="H257">
+        <v>95.3</v>
+      </c>
+      <c r="I257">
+        <f t="shared" si="8"/>
+        <v>21</v>
+      </c>
+      <c r="J257">
+        <v>540</v>
+      </c>
+      <c r="K257" s="2">
+        <f t="shared" si="9"/>
+        <v>38.888888888888886</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>8</v>
+      </c>
+      <c r="B258">
+        <v>360</v>
+      </c>
+      <c r="C258" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D258" t="s">
+        <v>13</v>
+      </c>
+      <c r="E258">
+        <v>90</v>
+      </c>
+      <c r="F258" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G258" t="s">
+        <v>7</v>
+      </c>
+      <c r="H258">
+        <v>119</v>
+      </c>
+      <c r="I258">
+        <f t="shared" si="8"/>
+        <v>26.25</v>
+      </c>
+      <c r="J258">
+        <v>540</v>
+      </c>
+      <c r="K258" s="2">
+        <f t="shared" si="9"/>
+        <v>48.611111111111114</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>8</v>
+      </c>
+      <c r="B259">
+        <v>360</v>
+      </c>
+      <c r="C259" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D259" t="s">
+        <v>13</v>
+      </c>
+      <c r="E259">
+        <v>90</v>
+      </c>
+      <c r="F259" s="1">
+        <v>3</v>
+      </c>
+      <c r="G259" t="s">
+        <v>7</v>
+      </c>
+      <c r="H259">
+        <v>143</v>
+      </c>
+      <c r="I259">
+        <f t="shared" si="8"/>
+        <v>31.5</v>
+      </c>
+      <c r="J259">
+        <v>540</v>
+      </c>
+      <c r="K259" s="2">
+        <f t="shared" si="9"/>
+        <v>58.333333333333336</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>8</v>
+      </c>
+      <c r="B260">
+        <v>360</v>
+      </c>
+      <c r="C260" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D260" t="s">
+        <v>13</v>
+      </c>
+      <c r="E260">
+        <v>90</v>
+      </c>
+      <c r="F260" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G260" t="s">
+        <v>7</v>
+      </c>
+      <c r="H260">
+        <v>167</v>
+      </c>
+      <c r="I260">
+        <f t="shared" si="8"/>
+        <v>36.75</v>
+      </c>
+      <c r="J260">
+        <v>540</v>
+      </c>
+      <c r="K260" s="2">
+        <f t="shared" si="9"/>
+        <v>68.055555555555557</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>8</v>
+      </c>
+      <c r="B261">
+        <v>360</v>
+      </c>
+      <c r="C261" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D261" t="s">
+        <v>13</v>
+      </c>
+      <c r="E261">
+        <v>90</v>
+      </c>
+      <c r="F261" s="1">
+        <v>4</v>
+      </c>
+      <c r="G261" t="s">
+        <v>7</v>
+      </c>
+      <c r="H261">
+        <v>191</v>
+      </c>
+      <c r="I261">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+      <c r="J261">
+        <v>540</v>
+      </c>
+      <c r="K261" s="2">
+        <f t="shared" si="9"/>
+        <v>77.777777777777771</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>8</v>
+      </c>
+      <c r="B262">
+        <v>360</v>
+      </c>
+      <c r="C262" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D262" t="s">
+        <v>13</v>
+      </c>
+      <c r="E262">
+        <v>90</v>
+      </c>
+      <c r="F262" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G262" t="s">
+        <v>7</v>
+      </c>
+      <c r="H262">
+        <v>214</v>
+      </c>
+      <c r="I262">
+        <f t="shared" si="8"/>
+        <v>47.25</v>
+      </c>
+      <c r="J262">
+        <v>540</v>
+      </c>
+      <c r="K262" s="2">
+        <f t="shared" si="9"/>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>8</v>
+      </c>
+      <c r="B263">
+        <v>360</v>
+      </c>
+      <c r="C263" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D263" t="s">
+        <v>13</v>
+      </c>
+      <c r="E263">
+        <v>90</v>
+      </c>
+      <c r="F263" s="1">
+        <v>5</v>
+      </c>
+      <c r="G263" t="s">
+        <v>7</v>
+      </c>
+      <c r="H263">
+        <v>238</v>
+      </c>
+      <c r="I263">
+        <f t="shared" si="8"/>
+        <v>52.5</v>
+      </c>
+      <c r="J263">
+        <v>540</v>
+      </c>
+      <c r="K263" s="2">
+        <f t="shared" si="9"/>
+        <v>97.222222222222229</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>8</v>
+      </c>
+      <c r="B264">
+        <v>360</v>
+      </c>
+      <c r="C264" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D264" t="s">
+        <v>13</v>
+      </c>
+      <c r="E264">
+        <v>90</v>
+      </c>
+      <c r="F264" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G264" t="s">
+        <v>7</v>
+      </c>
+      <c r="H264">
+        <v>262</v>
+      </c>
+      <c r="I264">
+        <f t="shared" si="8"/>
+        <v>57.75</v>
+      </c>
+      <c r="J264">
+        <v>540</v>
+      </c>
+      <c r="K264" s="2">
+        <f t="shared" si="9"/>
+        <v>106.94444444444444</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>8</v>
+      </c>
+      <c r="B265">
+        <v>360</v>
+      </c>
+      <c r="C265" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D265" t="s">
+        <v>13</v>
+      </c>
+      <c r="E265">
+        <v>90</v>
+      </c>
+      <c r="F265" s="1">
+        <v>6</v>
+      </c>
+      <c r="G265" t="s">
+        <v>7</v>
+      </c>
+      <c r="H265">
+        <v>286</v>
+      </c>
+      <c r="I265">
+        <f t="shared" si="8"/>
+        <v>63</v>
+      </c>
+      <c r="J265">
+        <v>540</v>
+      </c>
+      <c r="K265" s="2">
+        <f t="shared" si="9"/>
+        <v>116.66666666666667</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>8</v>
+      </c>
+      <c r="B266">
+        <v>360</v>
+      </c>
+      <c r="C266" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D266" t="s">
+        <v>13</v>
+      </c>
+      <c r="E266">
+        <v>90</v>
+      </c>
+      <c r="F266" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G266" t="s">
+        <v>7</v>
+      </c>
+      <c r="H266">
+        <v>310</v>
+      </c>
+      <c r="I266">
+        <f t="shared" si="8"/>
+        <v>68.25</v>
+      </c>
+      <c r="J266">
+        <v>540</v>
+      </c>
+      <c r="K266" s="2">
+        <f t="shared" si="9"/>
+        <v>126.38888888888889</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>8</v>
+      </c>
+      <c r="B267">
+        <v>360</v>
+      </c>
+      <c r="C267" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D267" t="s">
+        <v>13</v>
+      </c>
+      <c r="E267">
+        <v>90</v>
+      </c>
+      <c r="F267" s="1">
+        <v>7</v>
+      </c>
+      <c r="G267" t="s">
+        <v>7</v>
+      </c>
+      <c r="H267">
+        <v>334</v>
+      </c>
+      <c r="I267">
+        <f t="shared" ref="I267:I273" si="10">C267*F267</f>
+        <v>73.5</v>
+      </c>
+      <c r="J267">
+        <v>540</v>
+      </c>
+      <c r="K267" s="2">
+        <f t="shared" ref="K267:K273" si="11">1000*I267/J267</f>
+        <v>136.11111111111111</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>8</v>
+      </c>
+      <c r="B268">
+        <v>360</v>
+      </c>
+      <c r="C268" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D268" t="s">
+        <v>13</v>
+      </c>
+      <c r="E268">
+        <v>90</v>
+      </c>
+      <c r="F268" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G268" t="s">
+        <v>7</v>
+      </c>
+      <c r="H268">
+        <v>357</v>
+      </c>
+      <c r="I268">
+        <f t="shared" si="10"/>
+        <v>78.75</v>
+      </c>
+      <c r="J268">
+        <v>540</v>
+      </c>
+      <c r="K268" s="2">
+        <f t="shared" si="11"/>
+        <v>145.83333333333334</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>8</v>
+      </c>
+      <c r="B269">
+        <v>360</v>
+      </c>
+      <c r="C269" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D269" t="s">
+        <v>13</v>
+      </c>
+      <c r="E269">
+        <v>90</v>
+      </c>
+      <c r="F269" s="1">
+        <v>8</v>
+      </c>
+      <c r="G269" t="s">
+        <v>7</v>
+      </c>
+      <c r="H269">
+        <v>381</v>
+      </c>
+      <c r="I269">
+        <f t="shared" si="10"/>
+        <v>84</v>
+      </c>
+      <c r="J269">
+        <v>540</v>
+      </c>
+      <c r="K269" s="2">
+        <f t="shared" si="11"/>
+        <v>155.55555555555554</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>8</v>
+      </c>
+      <c r="B270">
+        <v>360</v>
+      </c>
+      <c r="C270" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D270" t="s">
+        <v>13</v>
+      </c>
+      <c r="E270">
+        <v>90</v>
+      </c>
+      <c r="F270" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G270" t="s">
+        <v>7</v>
+      </c>
+      <c r="H270">
+        <v>405</v>
+      </c>
+      <c r="I270">
+        <f t="shared" si="10"/>
+        <v>89.25</v>
+      </c>
+      <c r="J270">
+        <v>540</v>
+      </c>
+      <c r="K270" s="2">
+        <f t="shared" si="11"/>
+        <v>165.27777777777777</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>8</v>
+      </c>
+      <c r="B271">
+        <v>360</v>
+      </c>
+      <c r="C271" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D271" t="s">
+        <v>13</v>
+      </c>
+      <c r="E271">
+        <v>90</v>
+      </c>
+      <c r="F271" s="1">
+        <v>9</v>
+      </c>
+      <c r="G271" t="s">
+        <v>7</v>
+      </c>
+      <c r="H271">
+        <v>429</v>
+      </c>
+      <c r="I271">
+        <f t="shared" si="10"/>
+        <v>94.5</v>
+      </c>
+      <c r="J271">
+        <v>540</v>
+      </c>
+      <c r="K271" s="2">
+        <f t="shared" si="11"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>8</v>
+      </c>
+      <c r="B272">
+        <v>360</v>
+      </c>
+      <c r="C272" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D272" t="s">
+        <v>13</v>
+      </c>
+      <c r="E272">
+        <v>90</v>
+      </c>
+      <c r="F272" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="G272" t="s">
+        <v>7</v>
+      </c>
+      <c r="H272">
+        <v>453</v>
+      </c>
+      <c r="I272">
+        <f t="shared" si="10"/>
+        <v>99.75</v>
+      </c>
+      <c r="J272">
+        <v>540</v>
+      </c>
+      <c r="K272" s="2">
+        <f t="shared" si="11"/>
+        <v>184.72222222222223</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>8</v>
+      </c>
+      <c r="B273">
+        <v>360</v>
+      </c>
+      <c r="C273" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="D273" t="s">
+        <v>13</v>
+      </c>
+      <c r="E273">
+        <v>90</v>
+      </c>
+      <c r="F273" s="1">
+        <v>10</v>
+      </c>
+      <c r="G273" t="s">
+        <v>7</v>
+      </c>
+      <c r="H273">
+        <v>476</v>
+      </c>
+      <c r="I273">
+        <f t="shared" si="10"/>
+        <v>105</v>
+      </c>
+      <c r="J273">
+        <v>540</v>
+      </c>
+      <c r="K273" s="2">
+        <f t="shared" si="11"/>
         <v>194.44444444444446</v>
       </c>
     </row>

--- a/Modaliteter/FTV/accu_table.xlsx
+++ b/Modaliteter/FTV/accu_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\rvbrtg\Modaliteter\FTV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CFE62E-E614-4887-ABB3-CE68725BF1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D169B8-A626-4A31-889E-F64BF023EB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="20">
   <si>
     <t>Mode</t>
   </si>
@@ -88,6 +88,15 @@
   <si>
     <t>mmAs_per_frame</t>
   </si>
+  <si>
+    <t>bulk</t>
+  </si>
+  <si>
+    <t>gamla barn</t>
+  </si>
+  <si>
+    <t>nya barn?</t>
+  </si>
 </sst>
 </file>
 
@@ -105,12 +114,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -125,10 +140,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,12 +428,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K273"/>
+  <dimension ref="A1:M273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="7.5703125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="5.42578125" customWidth="1"/>
+    <col min="10" max="10" width="7.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2783,7 +2807,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -2820,7 +2844,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -2857,7 +2881,7 @@
         <v>170.00000000000003</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -2894,7 +2918,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -2931,44 +2955,48 @@
         <v>190.00000000000003</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>8</v>
-      </c>
-      <c r="B69">
-        <v>180</v>
-      </c>
-      <c r="C69" s="1">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="3">
+        <v>180</v>
+      </c>
+      <c r="C69" s="4">
         <v>5.4</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E69">
-        <v>85</v>
-      </c>
-      <c r="F69" s="1">
+      <c r="E69" s="3">
+        <v>85</v>
+      </c>
+      <c r="F69" s="4">
         <v>10</v>
       </c>
-      <c r="G69" t="s">
-        <v>7</v>
-      </c>
-      <c r="H69">
+      <c r="G69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H69" s="3">
         <v>215</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="3">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="J69">
+      <c r="J69" s="3">
         <v>270</v>
       </c>
-      <c r="K69" s="2">
+      <c r="K69" s="5">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M69" s="6"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -3005,7 +3033,7 @@
         <v>34.1796875</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -3042,7 +3070,7 @@
         <v>51.26953125</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>8</v>
       </c>
@@ -3079,7 +3107,7 @@
         <v>68.359375</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -3116,7 +3144,7 @@
         <v>85.44921875</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -3153,7 +3181,7 @@
         <v>102.5390625</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -3190,7 +3218,7 @@
         <v>119.62890625</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -3227,7 +3255,7 @@
         <v>136.71875</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -3264,7 +3292,7 @@
         <v>153.80859375</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -3301,7 +3329,7 @@
         <v>170.8984375</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -3338,7 +3366,7 @@
         <v>187.98828125</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -3375,7 +3403,7 @@
         <v>205.078125</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -3412,44 +3440,47 @@
         <v>222.16796875</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>8</v>
-      </c>
-      <c r="B82">
-        <v>360</v>
-      </c>
-      <c r="C82" s="1">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" s="3">
+        <v>360</v>
+      </c>
+      <c r="C82" s="4">
         <v>17.5</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E82">
-        <v>85</v>
-      </c>
-      <c r="F82" s="1">
-        <v>7</v>
-      </c>
-      <c r="G82" t="s">
-        <v>7</v>
-      </c>
-      <c r="H82">
+      <c r="E82" s="3">
+        <v>85</v>
+      </c>
+      <c r="F82" s="4">
+        <v>7</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H82" s="3">
         <v>489</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="3">
         <f t="shared" si="2"/>
         <v>122.5</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="3">
         <v>512</v>
       </c>
-      <c r="K82" s="2">
+      <c r="K82" s="5">
         <f t="shared" si="3"/>
         <v>239.2578125</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L82" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -3486,7 +3517,7 @@
         <v>256.34765625</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -3523,7 +3554,7 @@
         <v>273.4375</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -3560,7 +3591,7 @@
         <v>290.52734375</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -3597,7 +3628,7 @@
         <v>307.6171875</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -3634,7 +3665,7 @@
         <v>324.70703125</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -3671,7 +3702,7 @@
         <v>341.796875</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -3705,7 +3736,7 @@
         <v>33.809001097694839</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -3739,7 +3770,7 @@
         <v>50.713501646542262</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -3773,7 +3804,7 @@
         <v>67.618002195389678</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -3807,7 +3838,7 @@
         <v>84.522502744237102</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -3841,7 +3872,7 @@
         <v>101.42700329308452</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -3875,7 +3906,7 @@
         <v>118.33150384193195</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -3909,7 +3940,7 @@
         <v>135.23600439077936</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>8</v>
       </c>
@@ -4487,7 +4518,7 @@
         <v>249.19093851132686</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -4521,7 +4552,7 @@
         <v>274.11003236245955</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -4555,7 +4586,7 @@
         <v>299.02912621359224</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -4589,7 +4620,7 @@
         <v>323.94822006472498</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -4623,7 +4654,7 @@
         <v>348.86731391585761</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -4657,7 +4688,7 @@
         <v>373.78640776699029</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -4691,7 +4722,7 @@
         <v>398.70550161812298</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>8</v>
       </c>
@@ -4712,6 +4743,9 @@
       </c>
       <c r="G119" t="s">
         <v>7</v>
+      </c>
+      <c r="H119">
+        <v>41.9</v>
       </c>
       <c r="I119">
         <f t="shared" si="2"/>
@@ -4725,7 +4759,7 @@
         <v>19.444444444444443</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>8</v>
       </c>
@@ -4746,6 +4780,9 @@
       </c>
       <c r="G120" t="s">
         <v>7</v>
+      </c>
+      <c r="H120">
+        <v>62.9</v>
       </c>
       <c r="I120">
         <f t="shared" si="2"/>
@@ -4759,7 +4796,7 @@
         <v>29.166666666666668</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -4780,6 +4817,9 @@
       </c>
       <c r="G121" t="s">
         <v>7</v>
+      </c>
+      <c r="H121">
+        <v>83.9</v>
       </c>
       <c r="I121">
         <f t="shared" si="2"/>
@@ -4793,7 +4833,7 @@
         <v>38.888888888888886</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>8</v>
       </c>
@@ -4814,6 +4854,9 @@
       </c>
       <c r="G122" t="s">
         <v>7</v>
+      </c>
+      <c r="H122">
+        <v>105</v>
       </c>
       <c r="I122">
         <f t="shared" si="2"/>
@@ -4827,7 +4870,7 @@
         <v>48.611111111111114</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>8</v>
       </c>
@@ -4848,6 +4891,9 @@
       </c>
       <c r="G123" t="s">
         <v>7</v>
+      </c>
+      <c r="H123">
+        <v>126</v>
       </c>
       <c r="I123">
         <f t="shared" si="2"/>
@@ -4861,7 +4907,7 @@
         <v>58.333333333333336</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>8</v>
       </c>
@@ -4882,6 +4928,9 @@
       </c>
       <c r="G124" t="s">
         <v>7</v>
+      </c>
+      <c r="H124">
+        <v>147</v>
       </c>
       <c r="I124">
         <f t="shared" si="2"/>
@@ -4895,41 +4944,47 @@
         <v>68.055555555555557</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>8</v>
-      </c>
-      <c r="B125">
-        <v>360</v>
-      </c>
-      <c r="C125" s="1">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="3">
+        <v>360</v>
+      </c>
+      <c r="C125" s="4">
         <v>10.5</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E125">
-        <v>85</v>
-      </c>
-      <c r="F125" s="1">
+      <c r="E125" s="3">
+        <v>85</v>
+      </c>
+      <c r="F125" s="4">
         <v>4</v>
       </c>
-      <c r="G125" t="s">
-        <v>7</v>
-      </c>
-      <c r="I125">
+      <c r="G125" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H125" s="3">
+        <v>168</v>
+      </c>
+      <c r="I125" s="3">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="J125">
+      <c r="J125" s="3">
         <v>540</v>
       </c>
-      <c r="K125" s="2">
+      <c r="K125" s="5">
         <f t="shared" si="3"/>
         <v>77.777777777777771</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L125" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>8</v>
       </c>
@@ -4950,6 +5005,9 @@
       </c>
       <c r="G126" t="s">
         <v>7</v>
+      </c>
+      <c r="H126">
+        <v>189</v>
       </c>
       <c r="I126">
         <f t="shared" si="2"/>
@@ -4963,7 +5021,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>8</v>
       </c>
@@ -4984,6 +5042,9 @@
       </c>
       <c r="G127" t="s">
         <v>7</v>
+      </c>
+      <c r="H127">
+        <v>210</v>
       </c>
       <c r="I127">
         <f t="shared" si="2"/>
@@ -4997,7 +5058,7 @@
         <v>97.222222222222229</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -5018,6 +5079,9 @@
       </c>
       <c r="G128" t="s">
         <v>7</v>
+      </c>
+      <c r="H128">
+        <v>231</v>
       </c>
       <c r="I128">
         <f t="shared" si="2"/>
@@ -5053,6 +5117,9 @@
       <c r="G129" t="s">
         <v>7</v>
       </c>
+      <c r="H129">
+        <v>252</v>
+      </c>
       <c r="I129">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -5087,6 +5154,9 @@
       <c r="G130" t="s">
         <v>7</v>
       </c>
+      <c r="H130">
+        <v>273</v>
+      </c>
       <c r="I130">
         <f t="shared" si="2"/>
         <v>68.25</v>
@@ -5121,6 +5191,9 @@
       <c r="G131" t="s">
         <v>7</v>
       </c>
+      <c r="H131">
+        <v>294</v>
+      </c>
       <c r="I131">
         <f t="shared" ref="I131:I137" si="4">C131*F131</f>
         <v>73.5</v>
@@ -5155,6 +5228,9 @@
       <c r="G132" t="s">
         <v>7</v>
       </c>
+      <c r="H132">
+        <v>315</v>
+      </c>
       <c r="I132">
         <f t="shared" si="4"/>
         <v>78.75</v>
@@ -5189,6 +5265,9 @@
       <c r="G133" t="s">
         <v>7</v>
       </c>
+      <c r="H133">
+        <v>336</v>
+      </c>
       <c r="I133">
         <f t="shared" si="4"/>
         <v>84</v>
@@ -5223,6 +5302,9 @@
       <c r="G134" t="s">
         <v>7</v>
       </c>
+      <c r="H134">
+        <v>358</v>
+      </c>
       <c r="I134">
         <f t="shared" si="4"/>
         <v>89.25</v>
@@ -5257,6 +5339,9 @@
       <c r="G135" t="s">
         <v>7</v>
       </c>
+      <c r="H135">
+        <v>378</v>
+      </c>
       <c r="I135">
         <f t="shared" si="4"/>
         <v>94.5</v>
@@ -5291,6 +5376,9 @@
       <c r="G136" t="s">
         <v>7</v>
       </c>
+      <c r="H136">
+        <v>399</v>
+      </c>
       <c r="I136">
         <f t="shared" si="4"/>
         <v>99.75</v>
@@ -5325,6 +5413,9 @@
       <c r="G137" t="s">
         <v>7</v>
       </c>
+      <c r="H137">
+        <v>419</v>
+      </c>
       <c r="I137">
         <f t="shared" si="4"/>
         <v>105</v>
@@ -10219,38 +10310,38 @@
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>8</v>
-      </c>
-      <c r="B273">
-        <v>360</v>
-      </c>
-      <c r="C273" s="1">
+      <c r="A273" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B273" s="3">
+        <v>360</v>
+      </c>
+      <c r="C273" s="4">
         <v>10.5</v>
       </c>
-      <c r="D273" t="s">
+      <c r="D273" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E273">
-        <v>90</v>
-      </c>
-      <c r="F273" s="1">
+      <c r="E273" s="3">
+        <v>90</v>
+      </c>
+      <c r="F273" s="4">
         <v>10</v>
       </c>
-      <c r="G273" t="s">
-        <v>7</v>
-      </c>
-      <c r="H273">
+      <c r="G273" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H273" s="3">
         <v>476</v>
       </c>
-      <c r="I273">
+      <c r="I273" s="3">
         <f t="shared" si="10"/>
         <v>105</v>
       </c>
-      <c r="J273">
+      <c r="J273" s="3">
         <v>540</v>
       </c>
-      <c r="K273" s="2">
+      <c r="K273" s="5">
         <f t="shared" si="11"/>
         <v>194.44444444444446</v>
       </c>
